--- a/04_Figures/F5/c_data/F5.xlsx
+++ b/04_Figures/F5/c_data/F5.xlsx
@@ -686,7 +686,7 @@
     <t>01_Processing/07_Module_Characterisation/c_data/module_characterisation.xlsx</t>
   </si>
   <si>
-    <t>5e561cc796eef082629205d0768131b9</t>
+    <t>94cadc901960bff29e73192652852642</t>
   </si>
   <si>
     <t>modules</t>

--- a/04_Figures/F5/c_data/F5.xlsx
+++ b/04_Figures/F5/c_data/F5.xlsx
@@ -365,7 +365,7 @@
     <t>GOBP_ATP_SYNTHESIS_COUPLED_ELECTRON_TRANSPORT</t>
   </si>
   <si>
-    <t>ATP synthesis coupled electron ... (red)</t>
+    <t>ATP synthesis coupled electron transport (red)</t>
   </si>
   <si>
     <t>black</t>

--- a/04_Figures/F5/c_data/F5.xlsx
+++ b/04_Figures/F5/c_data/F5.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="324">
   <si>
     <t>sheet</t>
   </si>
@@ -317,25 +317,25 @@
     <t>turquoise</t>
   </si>
   <si>
-    <t>mRNA metabolic process</t>
-  </si>
-  <si>
-    <t>mRNA metabolic process (turquoise)</t>
+    <t>sulfur compound metabolic process</t>
+  </si>
+  <si>
+    <t>no set at FDR &lt; 0.05 (turquoise)</t>
   </si>
   <si>
     <t>blue</t>
   </si>
   <si>
-    <t>REACTOME_REGULATION_OF_PD_L1_CD274_POST_TRANSLATIONAL_MODIFICATION</t>
-  </si>
-  <si>
-    <t>no set at FDR &lt; 0.05 (blue)</t>
+    <t>REACTOME_MRNA_3_END_PROCESSING</t>
+  </si>
+  <si>
+    <t>mRNA 3 end processing (blue)</t>
   </si>
   <si>
     <t>brown</t>
   </si>
   <si>
-    <t>protein catabolic process</t>
+    <t>GOBP_ESTABLISHMENT_OF_PROTEIN_LOCALIZATION_TO_ORGANELLE</t>
   </si>
   <si>
     <t>no set at FDR &lt; 0.05 (brown)</t>
@@ -344,28 +344,28 @@
     <t>yellow</t>
   </si>
   <si>
-    <t>HALLMARK_EPITHELIAL_MESENCHYMAL_TRANSITION</t>
-  </si>
-  <si>
-    <t>Epithelial mesenchymal transition (yellow)</t>
+    <t>GOBP_PROTEIN_MODIFICATION_BY_SMALL_PROTEIN_REMOVAL</t>
+  </si>
+  <si>
+    <t>no set at FDR &lt; 0.05 (yellow)</t>
   </si>
   <si>
     <t>green</t>
   </si>
   <si>
-    <t>GOBP_PROTEIN_MODIFICATION_BY_SMALL_PROTEIN_REMOVAL</t>
-  </si>
-  <si>
-    <t>no set at FDR &lt; 0.05 (green)</t>
+    <t>cytoskeleton organization</t>
+  </si>
+  <si>
+    <t>Cytoskeleton organization (green)</t>
   </si>
   <si>
     <t>red</t>
   </si>
   <si>
-    <t>GOBP_ATP_SYNTHESIS_COUPLED_ELECTRON_TRANSPORT</t>
-  </si>
-  <si>
-    <t>ATP synthesis coupled electron transport (red)</t>
+    <t>REACTOME_AEROBIC_RESPIRATION_AND_RESPIRATORY_ELECTRON_TRANSPORT</t>
+  </si>
+  <si>
+    <t>Aerobic respiration and respiratory electron ... (red)</t>
   </si>
   <si>
     <t>black</t>
@@ -380,297 +380,279 @@
     <t>pink</t>
   </si>
   <si>
-    <t>KEGG_GLYCOLYSIS_GLUCONEOGENESIS</t>
-  </si>
-  <si>
-    <t>Glycolysis gluconeogenesis (pink)</t>
+    <t>GOBP_CARBOHYDRATE_CATABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t>Carbohydrate catabolic process (pink)</t>
   </si>
   <si>
     <t>magenta</t>
   </si>
   <si>
-    <t>inflammatory response</t>
-  </si>
-  <si>
-    <t>no set at FDR &lt; 0.05 (magenta)</t>
+    <t>REACTOME_CRISTAE_FORMATION</t>
+  </si>
+  <si>
+    <t>Cristae formation (magenta)</t>
   </si>
   <si>
     <t>purple</t>
   </si>
   <si>
-    <t>REACTOME_EUKARYOTIC_TRANSLATION_ELONGATION</t>
-  </si>
-  <si>
-    <t>Eukaryotic translation elongation (purple)</t>
+    <t>REACTOME_RESPONSE_OF_EIF2AK4_GCN2_TO_AMINO_ACID_DEFICIENCY</t>
+  </si>
+  <si>
+    <t>Response of EIF2AK4 GCN2 to amino acid defici... (purple)</t>
+  </si>
+  <si>
+    <t>Training_HR</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Training_LR</t>
+  </si>
+  <si>
+    <t>Acute_HR</t>
+  </si>
+  <si>
+    <t>Down</t>
+  </si>
+  <si>
+    <t>Acute_LR</t>
+  </si>
+  <si>
+    <t>Baseline_HRvLR</t>
+  </si>
+  <si>
+    <t>Trained_HRvLR</t>
+  </si>
+  <si>
+    <t>Acute_HRvLR</t>
+  </si>
+  <si>
+    <t>Training_Interaction</t>
+  </si>
+  <si>
+    <t>Acute_Interaction</t>
+  </si>
+  <si>
+    <t>S03_T1</t>
+  </si>
+  <si>
+    <t>HR_S03</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>S03_T2</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>S03_T3</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>S10_T1</t>
+  </si>
+  <si>
+    <t>HR_S10</t>
+  </si>
+  <si>
+    <t>S10_T2</t>
+  </si>
+  <si>
+    <t>S10_T3</t>
+  </si>
+  <si>
+    <t>S16_T1</t>
+  </si>
+  <si>
+    <t>HR_S16</t>
+  </si>
+  <si>
+    <t>S16_T2</t>
+  </si>
+  <si>
+    <t>S16_T3</t>
+  </si>
+  <si>
+    <t>S22_T1</t>
+  </si>
+  <si>
+    <t>HR_S22</t>
+  </si>
+  <si>
+    <t>S22_T2</t>
+  </si>
+  <si>
+    <t>S22_T3</t>
+  </si>
+  <si>
+    <t>S24_T1</t>
+  </si>
+  <si>
+    <t>HR_S24</t>
+  </si>
+  <si>
+    <t>S24_T2</t>
+  </si>
+  <si>
+    <t>S24_T3</t>
+  </si>
+  <si>
+    <t>S27_T1</t>
+  </si>
+  <si>
+    <t>HR_S27</t>
+  </si>
+  <si>
+    <t>S27_T2</t>
+  </si>
+  <si>
+    <t>S27_T3</t>
+  </si>
+  <si>
+    <t>S28_T1</t>
+  </si>
+  <si>
+    <t>HR_S28</t>
+  </si>
+  <si>
+    <t>S28_T2</t>
+  </si>
+  <si>
+    <t>S28_T3</t>
+  </si>
+  <si>
+    <t>S29_T1</t>
+  </si>
+  <si>
+    <t>HR_S29</t>
+  </si>
+  <si>
+    <t>S29_T2</t>
+  </si>
+  <si>
+    <t>S29_T3</t>
+  </si>
+  <si>
+    <t>S04_T1</t>
+  </si>
+  <si>
+    <t>LR_S04</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
+    <t>S04_T2</t>
+  </si>
+  <si>
+    <t>S04_T3</t>
+  </si>
+  <si>
+    <t>S05_T1</t>
+  </si>
+  <si>
+    <t>LR_S05</t>
+  </si>
+  <si>
+    <t>S05_T2</t>
+  </si>
+  <si>
+    <t>S05_T3</t>
+  </si>
+  <si>
+    <t>S06_T1</t>
+  </si>
+  <si>
+    <t>LR_S06</t>
+  </si>
+  <si>
+    <t>S06_T2</t>
+  </si>
+  <si>
+    <t>S06_T3</t>
+  </si>
+  <si>
+    <t>S12_T1</t>
+  </si>
+  <si>
+    <t>LR_S12</t>
+  </si>
+  <si>
+    <t>S12_T2</t>
+  </si>
+  <si>
+    <t>S12_T3</t>
+  </si>
+  <si>
+    <t>S14_T1</t>
+  </si>
+  <si>
+    <t>LR_S14</t>
+  </si>
+  <si>
+    <t>S14_T2</t>
+  </si>
+  <si>
+    <t>S14_T3</t>
+  </si>
+  <si>
+    <t>S17_T1</t>
+  </si>
+  <si>
+    <t>LR_S17</t>
+  </si>
+  <si>
+    <t>S17_T2</t>
+  </si>
+  <si>
+    <t>S17_T3</t>
+  </si>
+  <si>
+    <t>S21_T1</t>
+  </si>
+  <si>
+    <t>LR_S21</t>
+  </si>
+  <si>
+    <t>S21_T2</t>
+  </si>
+  <si>
+    <t>S21_T3</t>
+  </si>
+  <si>
+    <t>S30_T1</t>
+  </si>
+  <si>
+    <t>LR_S30</t>
+  </si>
+  <si>
+    <t>S30_T2</t>
+  </si>
+  <si>
+    <t>S30_T3</t>
   </si>
   <si>
     <t>greenyellow</t>
   </si>
   <si>
-    <t>REACTOME_GLYCOGEN_METABOLISM</t>
-  </si>
-  <si>
-    <t>Glycogen metabolism (greenyellow)</t>
+    <t>salmon</t>
   </si>
   <si>
     <t>tan</t>
   </si>
   <si>
-    <t>HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
-  </si>
-  <si>
-    <t>Oxidative phosphorylation (tan)</t>
-  </si>
-  <si>
-    <t>salmon</t>
-  </si>
-  <si>
-    <t>GOBP_KETONE_BIOSYNTHETIC_PROCESS</t>
-  </si>
-  <si>
-    <t>no set at FDR &lt; 0.05 (salmon)</t>
-  </si>
-  <si>
-    <t>Training_HR</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Training_LR</t>
-  </si>
-  <si>
-    <t>Acute_HR</t>
-  </si>
-  <si>
-    <t>Acute_LR</t>
-  </si>
-  <si>
-    <t>Baseline_HRvLR</t>
-  </si>
-  <si>
-    <t>Trained_HRvLR</t>
-  </si>
-  <si>
-    <t>Down</t>
-  </si>
-  <si>
-    <t>Acute_HRvLR</t>
-  </si>
-  <si>
-    <t>Training_Interaction</t>
-  </si>
-  <si>
-    <t>Acute_Interaction</t>
-  </si>
-  <si>
-    <t>S03_T1</t>
-  </si>
-  <si>
-    <t>HR_S03</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>S03_T2</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>S03_T3</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>S10_T1</t>
-  </si>
-  <si>
-    <t>HR_S10</t>
-  </si>
-  <si>
-    <t>S10_T2</t>
-  </si>
-  <si>
-    <t>S10_T3</t>
-  </si>
-  <si>
-    <t>S16_T1</t>
-  </si>
-  <si>
-    <t>HR_S16</t>
-  </si>
-  <si>
-    <t>S16_T2</t>
-  </si>
-  <si>
-    <t>S16_T3</t>
-  </si>
-  <si>
-    <t>S22_T1</t>
-  </si>
-  <si>
-    <t>HR_S22</t>
-  </si>
-  <si>
-    <t>S22_T2</t>
-  </si>
-  <si>
-    <t>S22_T3</t>
-  </si>
-  <si>
-    <t>S24_T1</t>
-  </si>
-  <si>
-    <t>HR_S24</t>
-  </si>
-  <si>
-    <t>S24_T2</t>
-  </si>
-  <si>
-    <t>S24_T3</t>
-  </si>
-  <si>
-    <t>S27_T1</t>
-  </si>
-  <si>
-    <t>HR_S27</t>
-  </si>
-  <si>
-    <t>S27_T2</t>
-  </si>
-  <si>
-    <t>S27_T3</t>
-  </si>
-  <si>
-    <t>S28_T1</t>
-  </si>
-  <si>
-    <t>HR_S28</t>
-  </si>
-  <si>
-    <t>S28_T2</t>
-  </si>
-  <si>
-    <t>S28_T3</t>
-  </si>
-  <si>
-    <t>S29_T1</t>
-  </si>
-  <si>
-    <t>HR_S29</t>
-  </si>
-  <si>
-    <t>S29_T2</t>
-  </si>
-  <si>
-    <t>S29_T3</t>
-  </si>
-  <si>
-    <t>S04_T1</t>
-  </si>
-  <si>
-    <t>LR_S04</t>
-  </si>
-  <si>
-    <t>LR</t>
-  </si>
-  <si>
-    <t>S04_T2</t>
-  </si>
-  <si>
-    <t>S04_T3</t>
-  </si>
-  <si>
-    <t>S05_T1</t>
-  </si>
-  <si>
-    <t>LR_S05</t>
-  </si>
-  <si>
-    <t>S05_T2</t>
-  </si>
-  <si>
-    <t>S05_T3</t>
-  </si>
-  <si>
-    <t>S06_T1</t>
-  </si>
-  <si>
-    <t>LR_S06</t>
-  </si>
-  <si>
-    <t>S06_T2</t>
-  </si>
-  <si>
-    <t>S06_T3</t>
-  </si>
-  <si>
-    <t>S12_T1</t>
-  </si>
-  <si>
-    <t>LR_S12</t>
-  </si>
-  <si>
-    <t>S12_T2</t>
-  </si>
-  <si>
-    <t>S12_T3</t>
-  </si>
-  <si>
-    <t>S14_T1</t>
-  </si>
-  <si>
-    <t>LR_S14</t>
-  </si>
-  <si>
-    <t>S14_T2</t>
-  </si>
-  <si>
-    <t>S14_T3</t>
-  </si>
-  <si>
-    <t>S17_T1</t>
-  </si>
-  <si>
-    <t>LR_S17</t>
-  </si>
-  <si>
-    <t>S17_T2</t>
-  </si>
-  <si>
-    <t>S17_T3</t>
-  </si>
-  <si>
-    <t>S21_T1</t>
-  </si>
-  <si>
-    <t>LR_S21</t>
-  </si>
-  <si>
-    <t>S21_T2</t>
-  </si>
-  <si>
-    <t>S21_T3</t>
-  </si>
-  <si>
-    <t>S30_T1</t>
-  </si>
-  <si>
-    <t>LR_S30</t>
-  </si>
-  <si>
-    <t>S30_T2</t>
-  </si>
-  <si>
-    <t>S30_T3</t>
-  </si>
-  <si>
     <t>midnightblue</t>
   </si>
   <si>
@@ -686,7 +668,7 @@
     <t>01_Processing/07_Module_Characterisation/c_data/module_characterisation.xlsx</t>
   </si>
   <si>
-    <t>94cadc901960bff29e73192652852642</t>
+    <t>344d4e14a48a06a4f63049c9e6502cfc</t>
   </si>
   <si>
     <t>modules</t>
@@ -695,7 +677,7 @@
     <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
-    <t>c9f0f1e2ec75a05e901fdd5ef1e6616c</t>
+    <t>32c36eae09056636394bdb0714dd608a</t>
   </si>
   <si>
     <t>module_tests</t>
@@ -704,7 +686,7 @@
     <t>02_HRvLR/03_Module_Contrasts/c_data/module_tests.rds</t>
   </si>
   <si>
-    <t>094819860069af034d3f46da223b5ebc</t>
+    <t>97324b049b076d735d54f0788a4c24d1</t>
   </si>
   <si>
     <t>preservation</t>
@@ -713,7 +695,7 @@
     <t>02_HRvLR/05_Module_Preservation/c_data/preservation.rds</t>
   </si>
   <si>
-    <t>907ecfde5eea48bd441e9d18c463766a</t>
+    <t>2ed523397dfe86c78388959c866dd3c3</t>
   </si>
   <si>
     <t>BiocManager</t>
@@ -1921,7 +1903,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1">
@@ -1961,31 +1943,31 @@
         <v>97</v>
       </c>
       <c r="B2">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="C2" t="s">
         <v>98</v>
       </c>
       <c r="D2">
-        <v>7.791209956661662E-06</v>
+        <v>0.9999998851201833</v>
       </c>
       <c r="E2" t="s">
         <v>99</v>
       </c>
       <c r="F2">
-        <v>1063</v>
+        <v>377</v>
       </c>
       <c r="G2">
-        <v>645</v>
+        <v>296</v>
       </c>
       <c r="H2">
-        <v>1.648062015503876</v>
+        <v>1.273648648648649</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3.17E-06</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.9625E-06</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1993,31 +1975,31 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="C3" t="s">
         <v>101</v>
       </c>
       <c r="D3">
-        <v>0.2505322957077189</v>
+        <v>9.912768757082083E-07</v>
       </c>
       <c r="E3" t="s">
         <v>102</v>
       </c>
       <c r="F3">
-        <v>403</v>
+        <v>988</v>
       </c>
       <c r="G3">
-        <v>350</v>
+        <v>576</v>
       </c>
       <c r="H3">
-        <v>1.151428571428571</v>
+        <v>1.715277777777778</v>
       </c>
       <c r="I3">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.004044444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2025,31 +2007,31 @@
         <v>103</v>
       </c>
       <c r="B4">
-        <v>148</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
         <v>104</v>
       </c>
       <c r="D4">
-        <v>0.9553572407915488</v>
+        <v>0.05980285799029572</v>
       </c>
       <c r="E4" t="s">
         <v>105</v>
       </c>
       <c r="F4">
-        <v>93</v>
+        <v>459</v>
       </c>
       <c r="G4">
-        <v>87</v>
+        <v>395</v>
       </c>
       <c r="H4">
-        <v>1.068965517241379</v>
+        <v>1.162025316455696</v>
       </c>
       <c r="I4">
-        <v>0.2788</v>
+        <v>0.00087</v>
       </c>
       <c r="J4">
-        <v>0.2788</v>
+        <v>0.0009666666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2057,31 +2039,31 @@
         <v>106</v>
       </c>
       <c r="B5">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
         <v>107</v>
       </c>
       <c r="D5">
-        <v>0.001020263978237809</v>
+        <v>0.1034468247763779</v>
       </c>
       <c r="E5" t="s">
         <v>108</v>
       </c>
       <c r="F5">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="G5">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="H5">
-        <v>4.037037037037037</v>
+        <v>1.447154471544716</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1.82E-06</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2.6E-06</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2089,31 +2071,31 @@
         <v>109</v>
       </c>
       <c r="B6">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
         <v>110</v>
       </c>
       <c r="D6">
-        <v>0.365564392839719</v>
+        <v>0.0004047356547587639</v>
       </c>
       <c r="E6" t="s">
         <v>111</v>
       </c>
       <c r="F6">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="G6">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H6">
-        <v>1.236842105263158</v>
+        <v>3.098039215686275</v>
       </c>
       <c r="I6">
-        <v>0.0948</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.1120363636363636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2121,25 +2103,25 @@
         <v>112</v>
       </c>
       <c r="B7">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
         <v>113</v>
       </c>
       <c r="D7">
-        <v>3.71815698342095E-47</v>
+        <v>6.477258366546305E-56</v>
       </c>
       <c r="E7" t="s">
         <v>114</v>
       </c>
       <c r="F7">
-        <v>1378</v>
+        <v>1948</v>
       </c>
       <c r="G7">
-        <v>299</v>
+        <v>602</v>
       </c>
       <c r="H7">
-        <v>4.608695652173913</v>
+        <v>3.235880398671096</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2153,25 +2135,25 @@
         <v>115</v>
       </c>
       <c r="B8">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
         <v>116</v>
       </c>
       <c r="D8">
-        <v>1.931190353245369E-27</v>
+        <v>1.848283754366588E-23</v>
       </c>
       <c r="E8" t="s">
         <v>117</v>
       </c>
       <c r="F8">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="G8">
         <v>57</v>
       </c>
       <c r="H8">
-        <v>8.368421052631579</v>
+        <v>7.578947368421052</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2185,25 +2167,25 @@
         <v>118</v>
       </c>
       <c r="B9">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
         <v>119</v>
       </c>
       <c r="D9">
-        <v>1.911362664565168E-10</v>
+        <v>1.763514044652909E-11</v>
       </c>
       <c r="E9" t="s">
         <v>120</v>
       </c>
       <c r="F9">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G9">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>3.191489361702128</v>
+        <v>4.323529411764706</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2217,31 +2199,31 @@
         <v>121</v>
       </c>
       <c r="B10">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>122</v>
       </c>
       <c r="D10">
-        <v>0.9760222589951819</v>
+        <v>0.0002356974046364792</v>
       </c>
       <c r="E10" t="s">
         <v>123</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>1.608695652173913</v>
+        <v>1.433333333333333</v>
       </c>
       <c r="I10">
-        <v>0.0039</v>
+        <v>0.0167</v>
       </c>
       <c r="J10">
-        <v>0.00507</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2249,127 +2231,31 @@
         <v>124</v>
       </c>
       <c r="B11">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>125</v>
       </c>
       <c r="D11">
-        <v>2.620511836975878E-32</v>
+        <v>8.890680033011591E-31</v>
       </c>
       <c r="E11" t="s">
         <v>126</v>
       </c>
       <c r="F11">
-        <v>988</v>
+        <v>695</v>
       </c>
       <c r="G11">
-        <v>412</v>
+        <v>277</v>
       </c>
       <c r="H11">
-        <v>2.398058252427184</v>
+        <v>2.509025270758123</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12">
-        <v>0.00119210505552338</v>
-      </c>
-      <c r="E12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F12">
-        <v>46</v>
-      </c>
-      <c r="G12">
-        <v>16</v>
-      </c>
-      <c r="H12">
-        <v>2.875</v>
-      </c>
-      <c r="I12">
-        <v>1.06E-09</v>
-      </c>
-      <c r="J12">
-        <v>1.7225E-09</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D13">
-        <v>8.246395938170626E-14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13">
-        <v>165</v>
-      </c>
-      <c r="G13">
-        <v>45</v>
-      </c>
-      <c r="H13">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B14">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14">
-        <v>0.5680510329287733</v>
-      </c>
-      <c r="E14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F14">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>12</v>
-      </c>
-      <c r="H14">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="I14">
-        <v>0.1498</v>
-      </c>
-      <c r="J14">
-        <v>0.1622833333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2379,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1">
@@ -2419,4097 +2305,3152 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2">
-        <v>-0.0054987691500267</v>
+        <v>0.0425633528623777</v>
       </c>
       <c r="D2">
-        <v>-0.1435679877537936</v>
+        <v>-0.0942707218077615</v>
       </c>
       <c r="E2">
-        <v>0.1325704494537402</v>
+        <v>0.1793974275325169</v>
       </c>
       <c r="F2">
-        <v>-0.0782355270466616</v>
+        <v>0.6114677783546695</v>
       </c>
       <c r="G2">
-        <v>0.9376700634223436</v>
+        <v>0.5412288265125489</v>
       </c>
       <c r="H2">
-        <v>0.9442169441935748</v>
+        <v>0.6765360331406861</v>
       </c>
       <c r="I2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J2">
-        <v>0.3861442352791007</v>
+        <v>0.1707946151798029</v>
       </c>
       <c r="K2">
-        <v>0.6274843823285386</v>
+        <v>0.5693153839326764</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
       </c>
       <c r="C3">
-        <v>0.07721069739113265</v>
+        <v>0.07610771121113491</v>
       </c>
       <c r="D3">
-        <v>-0.0622614689967988</v>
+        <v>-0.06213254205700333</v>
       </c>
       <c r="E3">
-        <v>0.2166828637790641</v>
+        <v>0.2143479644792732</v>
       </c>
       <c r="F3">
-        <v>1.087490121307166</v>
+        <v>1.0822463892001</v>
       </c>
       <c r="G3">
-        <v>0.2773117801520887</v>
+        <v>0.2797791541552769</v>
       </c>
       <c r="H3">
-        <v>0.6008421903295255</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J3">
-        <v>0.1577523362856363</v>
+        <v>0.0716406547401098</v>
       </c>
       <c r="K3">
-        <v>0.256347546464159</v>
+        <v>0.2388021824670327</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
       </c>
       <c r="C4">
-        <v>0.125593083680065</v>
+        <v>-0.04727770743448092</v>
       </c>
       <c r="D4">
-        <v>-0.01583623829026795</v>
+        <v>-0.1874793602858993</v>
       </c>
       <c r="E4">
-        <v>0.2670224056503979</v>
+        <v>0.09292394541693744</v>
       </c>
       <c r="F4">
-        <v>1.744462574551997</v>
+        <v>-0.662880555541783</v>
       </c>
       <c r="G4">
-        <v>0.0816548757673433</v>
+        <v>0.5077795386358084</v>
       </c>
       <c r="H4">
-        <v>0.2123026769950926</v>
+        <v>0.6400534327290553</v>
       </c>
       <c r="I4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J4">
-        <v>0.1047014469615506</v>
+        <v>0.3522420438937126</v>
       </c>
       <c r="K4">
-        <v>0.2268531350833597</v>
+        <v>0.6511028882641406</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
       </c>
       <c r="C5">
-        <v>0.0383491870575413</v>
+        <v>0.001028829222872507</v>
       </c>
       <c r="D5">
-        <v>-0.1240708801650519</v>
+        <v>-0.1601927318320653</v>
       </c>
       <c r="E5">
-        <v>0.2007692542801345</v>
+        <v>0.1622503902778103</v>
       </c>
       <c r="F5">
-        <v>0.4638225596410021</v>
+        <v>0.01254446586899491</v>
       </c>
       <c r="G5">
-        <v>0.6429642399292494</v>
+        <v>0.9899973285470545</v>
       </c>
       <c r="H5">
-        <v>0.8714899339990556</v>
+        <v>0.9899973285470545</v>
       </c>
       <c r="I5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J5">
-        <v>0.9109401183426684</v>
+        <v>0.4384909537784009</v>
       </c>
       <c r="K5">
-        <v>0.9549330940863852</v>
+        <v>0.7063355918429481</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
       </c>
       <c r="C6">
-        <v>0.0007363536410373989</v>
+        <v>-0.01393720418593809</v>
       </c>
       <c r="D6">
-        <v>-0.1418372820134943</v>
+        <v>-0.1569206936758</v>
       </c>
       <c r="E6">
-        <v>0.1433099892955692</v>
+        <v>0.1290462853039238</v>
       </c>
       <c r="F6">
-        <v>0.01014571378243173</v>
+        <v>-0.191611590429689</v>
       </c>
       <c r="G6">
-        <v>0.9919088267494406</v>
+        <v>0.8481413196956979</v>
       </c>
       <c r="H6">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I6" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J6">
-        <v>0.9353779908161459</v>
+        <v>0.5890489526110049</v>
       </c>
       <c r="K6">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
       </c>
       <c r="C7">
-        <v>-0.08197311290012195</v>
+        <v>-0.04748156253469531</v>
       </c>
       <c r="D7">
-        <v>-0.2257107102354681</v>
+        <v>-0.1916180669251236</v>
       </c>
       <c r="E7">
-        <v>0.06176448443522421</v>
+        <v>0.09665494185573296</v>
       </c>
       <c r="F7">
-        <v>-1.120305424019365</v>
+        <v>-0.6475644842426226</v>
       </c>
       <c r="G7">
-        <v>0.263088173725321</v>
+        <v>0.5176290985015108</v>
       </c>
       <c r="H7">
-        <v>0.5867252102342169</v>
+        <v>0.7394701407164441</v>
       </c>
       <c r="I7" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J7">
-        <v>0.6702682669121665</v>
+        <v>0.9021843720760001</v>
       </c>
       <c r="K7">
-        <v>0.9212483962173839</v>
+        <v>0.9694208397924868</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
       </c>
       <c r="C8">
-        <v>0.005270783722401737</v>
+        <v>-0.09578809919204873</v>
       </c>
       <c r="D8">
-        <v>-0.1407798647672876</v>
+        <v>-0.2422162337385044</v>
       </c>
       <c r="E8">
-        <v>0.151321432212091</v>
+        <v>0.05064003535440695</v>
       </c>
       <c r="F8">
-        <v>0.07089361110022646</v>
+        <v>-1.285935039802118</v>
       </c>
       <c r="G8">
-        <v>0.9435090197215235</v>
+        <v>0.1991914954412867</v>
       </c>
       <c r="H8">
-        <v>0.9435090197215235</v>
+        <v>0.4979787386032167</v>
       </c>
       <c r="I8" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J8">
-        <v>0.3325828813520937</v>
+        <v>0.9645036695830925</v>
       </c>
       <c r="K8">
-        <v>0.7232682404227637</v>
+        <v>0.9645036695830925</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
       </c>
       <c r="C9">
-        <v>-0.08270946654115935</v>
+        <v>-0.03354435834875721</v>
       </c>
       <c r="D9">
-        <v>-0.2775737495541141</v>
+        <v>-0.226660946943247</v>
       </c>
       <c r="E9">
-        <v>0.1121548164717953</v>
+        <v>0.1595722302457325</v>
       </c>
       <c r="F9">
-        <v>-0.8337932365972358</v>
+        <v>-0.3414537703865825</v>
       </c>
       <c r="G9">
-        <v>0.4047710105267779</v>
+        <v>0.732936929631133</v>
       </c>
       <c r="H9">
-        <v>0.6577528921060141</v>
+        <v>0.8143743662568145</v>
       </c>
       <c r="I9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J9">
-        <v>0.6948642645719122</v>
+        <v>0.7523072343854849</v>
       </c>
       <c r="K9">
-        <v>0.868457651346254</v>
+        <v>0.7933054336160084</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
       </c>
       <c r="C10">
-        <v>0.08724389662252371</v>
+        <v>-0.04830653665735343</v>
       </c>
       <c r="D10">
-        <v>-0.1145236459855779</v>
+        <v>-0.2483414839168158</v>
       </c>
       <c r="E10">
-        <v>0.2890114392306253</v>
+        <v>0.1517284106021089</v>
       </c>
       <c r="F10">
-        <v>0.8494134665561517</v>
+        <v>-0.4747139897352723</v>
       </c>
       <c r="G10">
-        <v>0.3960326155212974</v>
+        <v>0.6352435969063591</v>
       </c>
       <c r="H10">
-        <v>0.6435530002221084</v>
+        <v>0.7058262187848435</v>
       </c>
       <c r="I10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J10">
-        <v>0.2824575966805605</v>
+        <v>0.9487069974091134</v>
       </c>
       <c r="K10">
-        <v>0.8068623218637324</v>
+        <v>0.9487069974091134</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
         <v>100</v>
       </c>
       <c r="C11">
-        <v>-0.101470754095009</v>
+        <v>-0.006259927902483378</v>
       </c>
       <c r="D11">
-        <v>-0.2395399726987759</v>
+        <v>-0.1430940025726226</v>
       </c>
       <c r="E11">
-        <v>0.03659846450875795</v>
+        <v>0.1305741467676558</v>
       </c>
       <c r="F11">
-        <v>-1.443708166291483</v>
+        <v>-0.08993051415776293</v>
       </c>
       <c r="G11">
-        <v>0.1494085804277324</v>
+        <v>0.9283863474867411</v>
       </c>
       <c r="H11">
-        <v>0.6474371818535072</v>
+        <v>0.9442983937587401</v>
       </c>
       <c r="I11" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J11">
-        <v>0.5573323448634977</v>
+        <v>0.4745244109402941</v>
       </c>
       <c r="K11">
-        <v>0.6586654984750427</v>
+        <v>0.6045735119489917</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s">
         <v>100</v>
       </c>
       <c r="C12">
-        <v>0.04728881419753062</v>
+        <v>0.05704110385070692</v>
       </c>
       <c r="D12">
-        <v>-0.09218335219040083</v>
+        <v>-0.08119914941743131</v>
       </c>
       <c r="E12">
-        <v>0.1867609805854621</v>
+        <v>0.1952813571188452</v>
       </c>
       <c r="F12">
-        <v>0.6660491360106625</v>
+        <v>0.8111205513349317</v>
       </c>
       <c r="G12">
-        <v>0.5056678531363366</v>
+        <v>0.4177670470128998</v>
       </c>
       <c r="H12">
-        <v>0.66629387854546</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I12" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J12">
-        <v>0.1366189791388293</v>
+        <v>0.2792135560884471</v>
       </c>
       <c r="K12">
-        <v>0.2537209612578259</v>
+        <v>0.3490169451105589</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s">
         <v>100</v>
       </c>
       <c r="C13">
-        <v>0.05478062194202128</v>
+        <v>0.1351004258936614</v>
       </c>
       <c r="D13">
-        <v>-0.08664870002831167</v>
+        <v>-0.005101226957756999</v>
       </c>
       <c r="E13">
-        <v>0.1962099439123542</v>
+        <v>0.2753020787450797</v>
       </c>
       <c r="F13">
-        <v>0.7608917783400717</v>
+        <v>1.894242555953686</v>
       </c>
       <c r="G13">
-        <v>0.4470581919925174</v>
+        <v>0.05889633719271376</v>
       </c>
       <c r="H13">
-        <v>0.6457507217669696</v>
+        <v>0.2201229639232566</v>
       </c>
       <c r="I13" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J13">
-        <v>0.9458613915638576</v>
+        <v>0.04758100751936541</v>
       </c>
       <c r="K13">
-        <v>0.9458613915638576</v>
+        <v>0.182915392924374</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
         <v>100</v>
       </c>
       <c r="C14">
-        <v>-0.1080640070838788</v>
+        <v>0.0650280612752176</v>
       </c>
       <c r="D14">
-        <v>-0.2704840743064719</v>
+        <v>-0.09619349977972017</v>
       </c>
       <c r="E14">
-        <v>0.05435606013871444</v>
+        <v>0.2262496223301554</v>
       </c>
       <c r="F14">
-        <v>-1.307003569475967</v>
+        <v>0.7928840638063442</v>
       </c>
       <c r="G14">
-        <v>0.1917750885046281</v>
+        <v>0.4283039404333658</v>
       </c>
       <c r="H14">
-        <v>0.85010061097029</v>
+        <v>0.7176670345313296</v>
       </c>
       <c r="I14" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J14">
-        <v>0.009845690984578428</v>
+        <v>0.5741256834854711</v>
       </c>
       <c r="K14">
-        <v>0.04266466093317318</v>
+        <v>0.7176571043568389</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0.0313861439461532</v>
+        <v>-0.007903888844731727</v>
       </c>
       <c r="D15">
-        <v>-0.1111874917083785</v>
+        <v>-0.1508873783345936</v>
       </c>
       <c r="E15">
-        <v>0.1739597796006849</v>
+        <v>0.1350796006451302</v>
       </c>
       <c r="F15">
-        <v>0.4324482360992356</v>
+        <v>-0.1086643125775937</v>
       </c>
       <c r="G15">
-        <v>0.6655905761382903</v>
+        <v>0.9135219084195318</v>
       </c>
       <c r="H15">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J15">
-        <v>0.935657693159079</v>
+        <v>0.9457691952822583</v>
       </c>
       <c r="K15">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
         <v>100</v>
       </c>
       <c r="C16">
-        <v>-0.1173734243463864</v>
+        <v>-0.07120492059792202</v>
       </c>
       <c r="D16">
-        <v>-0.2611110216817326</v>
+        <v>-0.2153414249883503</v>
       </c>
       <c r="E16">
-        <v>0.02636417298895977</v>
+        <v>0.07293158379250625</v>
       </c>
       <c r="F16">
-        <v>-1.604112364150411</v>
+        <v>-0.9711091046937922</v>
       </c>
       <c r="G16">
-        <v>0.1092816363868238</v>
+        <v>0.3320664930220929</v>
       </c>
       <c r="H16">
-        <v>0.5867252102342169</v>
+        <v>0.6178168958284951</v>
       </c>
       <c r="I16" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J16">
-        <v>0.06828936357136127</v>
+        <v>0.6854971877349414</v>
       </c>
       <c r="K16">
-        <v>0.7375370848393966</v>
+        <v>0.9694208397924868</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0.04547120467951364</v>
+        <v>-0.001132555979478256</v>
       </c>
       <c r="D17">
-        <v>-0.1005794438101757</v>
+        <v>-0.1475606905259339</v>
       </c>
       <c r="E17">
-        <v>0.1915218531692029</v>
+        <v>0.1452955785669774</v>
       </c>
       <c r="F17">
-        <v>0.6116012476678389</v>
+        <v>-0.01520432528500775</v>
       </c>
       <c r="G17">
-        <v>0.5410623835904622</v>
+        <v>0.9878765667072451</v>
       </c>
       <c r="H17">
-        <v>0.706554485716153</v>
+        <v>0.9878765667072451</v>
       </c>
       <c r="I17" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J17">
-        <v>0.3330275168421853</v>
+        <v>0.3770034306424763</v>
       </c>
       <c r="K17">
-        <v>0.7232682404227637</v>
+        <v>0.6196861818806692</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
         <v>100</v>
       </c>
       <c r="C18">
-        <v>-0.1487595682925396</v>
+        <v>-0.0633010317531903</v>
       </c>
       <c r="D18">
-        <v>-0.3436238513054943</v>
+        <v>-0.25641762034768</v>
       </c>
       <c r="E18">
-        <v>0.04610471472041511</v>
+        <v>0.1298155568412994</v>
       </c>
       <c r="F18">
-        <v>-1.499643597141565</v>
+        <v>-0.644352046826032</v>
       </c>
       <c r="G18">
-        <v>0.1342988135418682</v>
+        <v>0.5197074916372459</v>
       </c>
       <c r="H18">
-        <v>0.6577528921060141</v>
+        <v>0.6496343645465574</v>
       </c>
       <c r="I18" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J18">
-        <v>0.1372844370162689</v>
+        <v>0.7933054336160084</v>
       </c>
       <c r="K18">
-        <v>0.6204836166502532</v>
+        <v>0.7933054336160084</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
         <v>100</v>
       </c>
       <c r="C19">
-        <v>0.1628446290259</v>
+        <v>0.07007236461844377</v>
       </c>
       <c r="D19">
-        <v>-0.0389229135822016</v>
+        <v>-0.1299625826410186</v>
       </c>
       <c r="E19">
-        <v>0.3646121716340016</v>
+        <v>0.2701073118779062</v>
       </c>
       <c r="F19">
-        <v>1.585468166895581</v>
+        <v>0.6886093286744153</v>
       </c>
       <c r="G19">
-        <v>0.113453084050392</v>
+        <v>0.491458601310655</v>
       </c>
       <c r="H19">
-        <v>0.5115858867864171</v>
+        <v>0.6567494695136065</v>
       </c>
       <c r="I19" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J19">
-        <v>0.03789215525515411</v>
+        <v>0.3223905699002036</v>
       </c>
       <c r="K19">
-        <v>0.4657134339440013</v>
+        <v>0.7637718376832046</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B20" t="s">
         <v>103</v>
       </c>
       <c r="C20">
-        <v>0.08130146707719085</v>
+        <v>-0.1047455003627971</v>
       </c>
       <c r="D20">
-        <v>-0.05676775152657607</v>
+        <v>-0.2415795750329363</v>
       </c>
       <c r="E20">
-        <v>0.2193706856809578</v>
+        <v>0.03208857430734209</v>
       </c>
       <c r="F20">
-        <v>1.156743073387605</v>
+        <v>-1.504780382470787</v>
       </c>
       <c r="G20">
-        <v>0.2478955145941231</v>
+        <v>0.1331504927352704</v>
       </c>
       <c r="H20">
-        <v>0.6655565179269085</v>
+        <v>0.4438349757842345</v>
       </c>
       <c r="I20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J20">
-        <v>0.1162861974157408</v>
+        <v>0.5441161607540925</v>
       </c>
       <c r="K20">
-        <v>0.4044997352781564</v>
+        <v>0.6045735119489917</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B21" t="s">
         <v>103</v>
       </c>
       <c r="C21">
-        <v>0.04826592436045607</v>
+        <v>0.04440447083962451</v>
       </c>
       <c r="D21">
-        <v>-0.09120624202747538</v>
+        <v>-0.09383578242851373</v>
       </c>
       <c r="E21">
-        <v>0.1877380907483875</v>
+        <v>0.1826447241077628</v>
       </c>
       <c r="F21">
-        <v>0.6798114472643398</v>
+        <v>0.6314285039686475</v>
       </c>
       <c r="G21">
-        <v>0.4969189966281227</v>
+        <v>0.5281122529078924</v>
       </c>
       <c r="H21">
-        <v>0.66629387854546</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I21" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J21">
-        <v>0.3420538450470071</v>
+        <v>0.1461770367776989</v>
       </c>
       <c r="K21">
-        <v>0.404245453237372</v>
+        <v>0.2923540735553978</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s">
         <v>103</v>
       </c>
       <c r="C22">
-        <v>-0.06817316243779101</v>
+        <v>0.06016949484280429</v>
       </c>
       <c r="D22">
-        <v>-0.209602484408124</v>
+        <v>-0.08003215800861407</v>
       </c>
       <c r="E22">
-        <v>0.07325615953254194</v>
+        <v>0.2003711476942227</v>
       </c>
       <c r="F22">
-        <v>-0.9469114618168828</v>
+        <v>0.8436362576028211</v>
       </c>
       <c r="G22">
-        <v>0.3441129866372323</v>
+        <v>0.3993646269456278</v>
       </c>
       <c r="H22">
-        <v>0.5591836032855025</v>
+        <v>0.6400534327290553</v>
       </c>
       <c r="I22" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J22">
-        <v>0.5353991814892595</v>
+        <v>0.8951900195200588</v>
       </c>
       <c r="K22">
-        <v>0.8648600795345258</v>
+        <v>0.9003841440817234</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s">
         <v>103</v>
       </c>
       <c r="C23">
-        <v>0.05365068328857855</v>
+        <v>-0.1066264770652267</v>
       </c>
       <c r="D23">
-        <v>-0.1087693839340146</v>
+        <v>-0.2678480381201644</v>
       </c>
       <c r="E23">
-        <v>0.2160707505111717</v>
+        <v>0.05459508398971108</v>
       </c>
       <c r="F23">
-        <v>0.648889824236933</v>
+        <v>-1.300091572575458</v>
       </c>
       <c r="G23">
-        <v>0.5166890768489223</v>
+        <v>0.1942999707063497</v>
       </c>
       <c r="H23">
-        <v>0.8714899339990556</v>
+        <v>0.7176670345313296</v>
       </c>
       <c r="I23" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J23">
-        <v>0.5830948964205924</v>
+        <v>0.009443357819857296</v>
       </c>
       <c r="K23">
-        <v>0.7580233653467702</v>
+        <v>0.03314362828753616</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
         <v>103</v>
       </c>
       <c r="C24">
-        <v>-0.02421621669891974</v>
+        <v>0.03043325385963299</v>
       </c>
       <c r="D24">
-        <v>-0.1667898523534515</v>
+        <v>-0.1125502356302289</v>
       </c>
       <c r="E24">
-        <v>0.118357418955612</v>
+        <v>0.1734167433494949</v>
       </c>
       <c r="F24">
-        <v>-0.3336587066704069</v>
+        <v>0.418402722396669</v>
       </c>
       <c r="G24">
-        <v>0.7387683363069686</v>
+        <v>0.6758717668559306</v>
       </c>
       <c r="H24">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I24" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J24">
-        <v>0.7018089091990904</v>
+        <v>0.9694454941851673</v>
       </c>
       <c r="K24">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
         <v>103</v>
       </c>
       <c r="C25">
-        <v>0.00881932601781505</v>
+        <v>-0.1187167173427886</v>
       </c>
       <c r="D25">
-        <v>-0.1349182713175311</v>
+        <v>-0.2628532217332169</v>
       </c>
       <c r="E25">
-        <v>0.1525569233531612</v>
+        <v>0.02541978704763964</v>
       </c>
       <c r="F25">
-        <v>0.1205314575035323</v>
+        <v>-1.619085930057282</v>
       </c>
       <c r="G25">
-        <v>0.90410758308882</v>
+        <v>0.1061977009712752</v>
       </c>
       <c r="H25">
-        <v>0.90410758308882</v>
+        <v>0.5309885048563763</v>
       </c>
       <c r="I25" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J25">
-        <v>0.3337965965680105</v>
+        <v>0.06411506355543335</v>
       </c>
       <c r="K25">
-        <v>0.9212483962173839</v>
+        <v>0.6411506355543335</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
         <v>103</v>
       </c>
       <c r="C26">
-        <v>-0.1130045197085545</v>
+        <v>0.04807925456524235</v>
       </c>
       <c r="D26">
-        <v>-0.2590551681982438</v>
+        <v>-0.09834887998121333</v>
       </c>
       <c r="E26">
-        <v>0.0330461287811348</v>
+        <v>0.194507389111698</v>
       </c>
       <c r="F26">
-        <v>-1.519944451284682</v>
+        <v>0.6454538575721446</v>
       </c>
       <c r="G26">
-        <v>0.1291178969865852</v>
+        <v>0.5189941520019834</v>
       </c>
       <c r="H26">
-        <v>0.3357065321651216</v>
+        <v>0.7414202171456906</v>
       </c>
       <c r="I26" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J26">
-        <v>0.8503008912428012</v>
+        <v>0.3086863415168629</v>
       </c>
       <c r="K26">
-        <v>0.9211592988463678</v>
+        <v>0.6196861818806692</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
         <v>103</v>
       </c>
       <c r="C27">
-        <v>0.03303554271673479</v>
+        <v>-0.1491499712024216</v>
       </c>
       <c r="D27">
-        <v>-0.1618287402962199</v>
+        <v>-0.3422665597969113</v>
       </c>
       <c r="E27">
-        <v>0.2278998257296895</v>
+        <v>0.04396661739206811</v>
       </c>
       <c r="F27">
-        <v>0.333030948408127</v>
+        <v>-1.518223108953995</v>
       </c>
       <c r="G27">
-        <v>0.7392418765620605</v>
+        <v>0.1297288510577531</v>
       </c>
       <c r="H27">
-        <v>0.8736494904824352</v>
+        <v>0.6486442552887656</v>
       </c>
       <c r="I27" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J27">
-        <v>0.6449661313849585</v>
+        <v>0.140610429977404</v>
       </c>
       <c r="K27">
-        <v>0.868457651346254</v>
+        <v>0.4687014332580133</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
         <v>103</v>
       </c>
       <c r="C28">
-        <v>-0.1218238457263696</v>
+        <v>0.166795971908031</v>
       </c>
       <c r="D28">
-        <v>-0.3235913883344712</v>
+        <v>-0.03323897535143139</v>
       </c>
       <c r="E28">
-        <v>0.07994369688173206</v>
+        <v>0.3668309191674933</v>
       </c>
       <c r="F28">
-        <v>-1.186086581567499</v>
+        <v>1.639123538453478</v>
       </c>
       <c r="G28">
-        <v>0.2361165631321926</v>
+        <v>0.1019545904639061</v>
       </c>
       <c r="H28">
-        <v>0.5115858867864171</v>
+        <v>0.5097729523195305</v>
       </c>
       <c r="I28" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J28">
-        <v>0.3815815555554462</v>
+        <v>0.03296450659402272</v>
       </c>
       <c r="K28">
-        <v>0.8068623218637324</v>
+        <v>0.3296450659402272</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s">
         <v>106</v>
       </c>
       <c r="C29">
-        <v>-0.004920199100966258</v>
+        <v>-0.06276873429032612</v>
       </c>
       <c r="D29">
-        <v>-0.1429894177047332</v>
+        <v>-0.1996028089604653</v>
       </c>
       <c r="E29">
-        <v>0.1331490195028007</v>
+        <v>0.07406534037981308</v>
       </c>
       <c r="F29">
-        <v>-0.07000373344218982</v>
+        <v>-0.9017395464765133</v>
       </c>
       <c r="G29">
-        <v>0.9442169441935748</v>
+        <v>0.3677246497264625</v>
       </c>
       <c r="H29">
-        <v>0.9442169441935748</v>
+        <v>0.6128744162107708</v>
       </c>
       <c r="I29" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J29">
-        <v>0.5205040836140331</v>
+        <v>0.9545893326380187</v>
       </c>
       <c r="K29">
-        <v>0.6586654984750427</v>
+        <v>0.9545893326380187</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
         <v>106</v>
       </c>
       <c r="C30">
-        <v>0.0967824778134018</v>
+        <v>0.09786453835089065</v>
       </c>
       <c r="D30">
-        <v>-0.04268968857452965</v>
+        <v>-0.04037571491724759</v>
       </c>
       <c r="E30">
-        <v>0.2362546442013332</v>
+        <v>0.2361047916190289</v>
       </c>
       <c r="F30">
-        <v>1.363152932093474</v>
+        <v>1.391626966250044</v>
       </c>
       <c r="G30">
-        <v>0.1734098680058355</v>
+        <v>0.1647899189803771</v>
       </c>
       <c r="H30">
-        <v>0.6008421903295255</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I30" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J30">
-        <v>0.2676710216319668</v>
+        <v>0.02583659267413433</v>
       </c>
       <c r="K30">
-        <v>0.36711697372125</v>
+        <v>0.2388021824670327</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
         <v>106</v>
       </c>
       <c r="C31">
-        <v>0.03193864141879552</v>
+        <v>0.03104254581840267</v>
       </c>
       <c r="D31">
-        <v>-0.1094906805515374</v>
+        <v>-0.1091591070330157</v>
       </c>
       <c r="E31">
-        <v>0.1733679633891285</v>
+        <v>0.171244198669821</v>
       </c>
       <c r="F31">
-        <v>0.4436212807630002</v>
+        <v>0.4352474164710932</v>
       </c>
       <c r="G31">
-        <v>0.6574964419280021</v>
+        <v>0.6636118735888674</v>
       </c>
       <c r="H31">
-        <v>0.7122878120886689</v>
+        <v>0.6636118735888674</v>
       </c>
       <c r="I31" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J31">
-        <v>0.8999887393765725</v>
+        <v>0.6075779845994707</v>
       </c>
       <c r="K31">
-        <v>0.9458613915638576</v>
+        <v>0.7594724807493383</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B32" t="s">
         <v>106</v>
       </c>
       <c r="C32">
-        <v>-0.07012866859908842</v>
+        <v>-0.09652779034819252</v>
       </c>
       <c r="D32">
-        <v>-0.2325487358216816</v>
+        <v>-0.2577493514031303</v>
       </c>
       <c r="E32">
-        <v>0.09229139862350477</v>
+        <v>0.06469377070674524</v>
       </c>
       <c r="F32">
-        <v>-0.8481863911492834</v>
+        <v>-1.176958764887699</v>
       </c>
       <c r="G32">
-        <v>0.3967149129481858</v>
+        <v>0.2398947814553622</v>
       </c>
       <c r="H32">
-        <v>0.8714899339990556</v>
+        <v>0.7176670345313296</v>
       </c>
       <c r="I32" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J32">
-        <v>0.3711037460746972</v>
+        <v>0.008502348303124092</v>
       </c>
       <c r="K32">
-        <v>0.6847797609201389</v>
+        <v>0.03314362828753616</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B33" t="s">
         <v>106</v>
       </c>
       <c r="C33">
-        <v>0.02776000707440014</v>
+        <v>0.01441653509186119</v>
       </c>
       <c r="D33">
-        <v>-0.1148136285801316</v>
+        <v>-0.1285669543980007</v>
       </c>
       <c r="E33">
-        <v>0.1703336427289319</v>
+        <v>0.1574000245817231</v>
       </c>
       <c r="F33">
-        <v>0.3824861733261116</v>
+        <v>0.1982015317120803</v>
       </c>
       <c r="G33">
-        <v>0.7022532521797367</v>
+        <v>0.842985625068342</v>
       </c>
       <c r="H33">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I33" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J33">
-        <v>0.6235160407364819</v>
+        <v>0.5975685912179473</v>
       </c>
       <c r="K33">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B34" t="s">
         <v>106</v>
       </c>
       <c r="C34">
-        <v>-0.07394266983996792</v>
+        <v>-0.1462167375493556</v>
       </c>
       <c r="D34">
-        <v>-0.2176802671753141</v>
+        <v>-0.2903532419397838</v>
       </c>
       <c r="E34">
-        <v>0.06979492749537825</v>
+        <v>-0.002080233158927303</v>
       </c>
       <c r="F34">
-        <v>-1.010555426742442</v>
+        <v>-1.994137538536145</v>
       </c>
       <c r="G34">
-        <v>0.3126877869251271</v>
+        <v>0.04679887980401823</v>
       </c>
       <c r="H34">
-        <v>0.5867252102342169</v>
+        <v>0.4679887980401823</v>
       </c>
       <c r="I34" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J34">
-        <v>0.9532280477263078</v>
+        <v>0.1316159069109117</v>
       </c>
       <c r="K34">
-        <v>0.9587258105901777</v>
+        <v>0.6580795345545583</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B35" t="s">
         <v>106</v>
       </c>
       <c r="C35">
-        <v>0.02812464017791602</v>
+        <v>-0.01864640138276039</v>
       </c>
       <c r="D35">
-        <v>-0.1179260083117733</v>
+        <v>-0.1650745359292161</v>
       </c>
       <c r="E35">
-        <v>0.1741752886676053</v>
+        <v>0.1277817331636953</v>
       </c>
       <c r="F35">
-        <v>0.378284788016011</v>
+        <v>-0.2503240079566862</v>
       </c>
       <c r="G35">
-        <v>0.7053696594632073</v>
+        <v>0.8024621773562708</v>
       </c>
       <c r="H35">
-        <v>0.8336186884565178</v>
+        <v>0.8916246415069676</v>
       </c>
       <c r="I35" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J35">
-        <v>0.4065700188023368</v>
+        <v>0.4331871894785154</v>
       </c>
       <c r="K35">
-        <v>0.7232682404227637</v>
+        <v>0.6196861818806692</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s">
         <v>106</v>
       </c>
       <c r="C36">
-        <v>-0.1017026769143681</v>
+        <v>-0.1606332726412168</v>
       </c>
       <c r="D36">
-        <v>-0.2965669599273227</v>
+        <v>-0.3537498612357065</v>
       </c>
       <c r="E36">
-        <v>0.09316160609858663</v>
+        <v>0.03248331595327297</v>
       </c>
       <c r="F36">
-        <v>-1.02526358470508</v>
+        <v>-1.635113601596479</v>
       </c>
       <c r="G36">
-        <v>0.3057039096351724</v>
+        <v>0.1027927054997094</v>
       </c>
       <c r="H36">
-        <v>0.6577528921060141</v>
+        <v>0.6486442552887656</v>
       </c>
       <c r="I36" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J36">
-        <v>0.7348487819083687</v>
+        <v>0.1153198457299659</v>
       </c>
       <c r="K36">
-        <v>0.868457651346254</v>
+        <v>0.4687014332580133</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B37" t="s">
         <v>106</v>
       </c>
       <c r="C37">
-        <v>0.1020673100178839</v>
+        <v>0.1275703361665952</v>
       </c>
       <c r="D37">
-        <v>-0.09970023259021768</v>
+        <v>-0.07246461109286717</v>
       </c>
       <c r="E37">
-        <v>0.3038348526259855</v>
+        <v>0.3276052834260575</v>
       </c>
       <c r="F37">
-        <v>0.9937353898744775</v>
+        <v>1.253648624886373</v>
       </c>
       <c r="G37">
-        <v>0.3208026237634016</v>
+        <v>0.2106841166938012</v>
       </c>
       <c r="H37">
-        <v>0.5957763012748888</v>
+        <v>0.5267102917345029</v>
       </c>
       <c r="I37" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J37">
-        <v>0.5268149745254</v>
+        <v>0.08343471238071162</v>
       </c>
       <c r="K37">
-        <v>0.8068623218637324</v>
+        <v>0.4171735619035581</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38">
-        <v>-0.06757620632004468</v>
+        <v>-0.004866416169759566</v>
       </c>
       <c r="D38">
-        <v>-0.2056454249238116</v>
+        <v>-0.1417004908398988</v>
       </c>
       <c r="E38">
-        <v>0.07049301228372223</v>
+        <v>0.1319676585003796</v>
       </c>
       <c r="F38">
-        <v>-0.9614624606012001</v>
+        <v>-0.06991123780810848</v>
       </c>
       <c r="G38">
-        <v>0.3367556565546066</v>
+        <v>0.9442983937587401</v>
       </c>
       <c r="H38">
-        <v>0.6890380576592875</v>
+        <v>0.9442983937587401</v>
       </c>
       <c r="I38" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J38">
-        <v>0.9965938805365767</v>
+        <v>0.5206533678299929</v>
       </c>
       <c r="K38">
-        <v>0.9965938805365767</v>
+        <v>0.6045735119489917</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39">
-        <v>0.08706861522807155</v>
+        <v>0.1068657419990231</v>
       </c>
       <c r="D39">
-        <v>-0.0524035511598599</v>
+        <v>-0.0313745112691151</v>
       </c>
       <c r="E39">
-        <v>0.226540781616003</v>
+        <v>0.2451059952671614</v>
       </c>
       <c r="F39">
-        <v>1.226336014772182</v>
+        <v>1.519623459530753</v>
       </c>
       <c r="G39">
-        <v>0.2206137463813437</v>
+        <v>0.1293763897862113</v>
       </c>
       <c r="H39">
-        <v>0.6008421903295255</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I39" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J39">
-        <v>0.04144087878871429</v>
+        <v>0.229149968652484</v>
       </c>
       <c r="K39">
-        <v>0.1795771414177619</v>
+        <v>0.3273570980749771</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40">
-        <v>0.03888309711717415</v>
+        <v>0.04680354706877332</v>
       </c>
       <c r="D40">
-        <v>-0.1025462248531588</v>
+        <v>-0.09339810578264504</v>
       </c>
       <c r="E40">
-        <v>0.1803124190875071</v>
+        <v>0.1870051999201917</v>
       </c>
       <c r="F40">
-        <v>0.5400783682990932</v>
+        <v>0.6562323548634458</v>
       </c>
       <c r="G40">
-        <v>0.5893685658684462</v>
+        <v>0.5120427461832443</v>
       </c>
       <c r="H40">
-        <v>0.6965264869354365</v>
+        <v>0.6400534327290553</v>
       </c>
       <c r="I40" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J40">
-        <v>0.6957085375917975</v>
+        <v>0.9003841440817234</v>
       </c>
       <c r="K40">
-        <v>0.8648600795345258</v>
+        <v>0.9003841440817234</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41">
-        <v>-0.0965033193675965</v>
+        <v>-0.06383957625956076</v>
       </c>
       <c r="D41">
-        <v>-0.2589233865901897</v>
+        <v>-0.2250611373144985</v>
       </c>
       <c r="E41">
-        <v>0.0659167478549967</v>
+        <v>0.09738198479537701</v>
       </c>
       <c r="F41">
-        <v>-1.167180324729456</v>
+        <v>-0.7783929224358715</v>
       </c>
       <c r="G41">
-        <v>0.2436594545226432</v>
+        <v>0.4367863884379893</v>
       </c>
       <c r="H41">
-        <v>0.85010061097029</v>
+        <v>0.7176670345313296</v>
       </c>
       <c r="I41" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J41">
-        <v>0.008920757107900711</v>
+        <v>0.4511931021422798</v>
       </c>
       <c r="K41">
-        <v>0.04266466093317318</v>
+        <v>0.7063355918429481</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42">
-        <v>0.009521468244521058</v>
+        <v>0.02986815773245619</v>
       </c>
       <c r="D42">
-        <v>-0.1330521674100107</v>
+        <v>-0.1131153317574057</v>
       </c>
       <c r="E42">
-        <v>0.1520951038990528</v>
+        <v>0.1728516472223181</v>
       </c>
       <c r="F42">
-        <v>0.1311898063834209</v>
+        <v>0.4106336629619761</v>
       </c>
       <c r="G42">
-        <v>0.8956746616568585</v>
+        <v>0.6815556903267269</v>
       </c>
       <c r="H42">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I42" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J42">
-        <v>0.7523546069009029</v>
+        <v>0.5811158301083822</v>
       </c>
       <c r="K42">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43">
-        <v>-0.1451233533035952</v>
+        <v>-0.08186400043632652</v>
       </c>
       <c r="D43">
-        <v>-0.2888609506389413</v>
+        <v>-0.2260005048267548</v>
       </c>
       <c r="E43">
-        <v>-0.001385755968249025</v>
+        <v>0.06227250395410175</v>
       </c>
       <c r="F43">
-        <v>-1.983363496955285</v>
+        <v>-1.116480090179235</v>
       </c>
       <c r="G43">
-        <v>0.04783956641540919</v>
+        <v>0.2648705675787603</v>
       </c>
       <c r="H43">
-        <v>0.5867252102342169</v>
+        <v>0.6178168958284951</v>
       </c>
       <c r="I43" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J43">
-        <v>0.1134672438214456</v>
+        <v>0.9694208397924868</v>
       </c>
       <c r="K43">
-        <v>0.7375370848393966</v>
+        <v>0.9694208397924868</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44">
-        <v>-0.009736936818824532</v>
+        <v>0.02877912289200756</v>
       </c>
       <c r="D44">
-        <v>-0.1557875853085139</v>
+        <v>-0.1176490116544481</v>
       </c>
       <c r="E44">
-        <v>0.1363137116708648</v>
+        <v>0.1752072574384632</v>
       </c>
       <c r="F44">
-        <v>-0.1309647006018073</v>
+        <v>0.3863536582702727</v>
       </c>
       <c r="G44">
-        <v>0.8958526473964914</v>
+        <v>0.6994351853897671</v>
       </c>
       <c r="H44">
-        <v>0.9435090197215235</v>
+        <v>0.8742939817372088</v>
       </c>
       <c r="I44" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J44">
-        <v>0.4178096969981739</v>
+        <v>0.3698540707387067</v>
       </c>
       <c r="K44">
-        <v>0.7232682404227637</v>
+        <v>0.6196861818806692</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45">
-        <v>-0.1546448215481162</v>
+        <v>-0.1117321581687827</v>
       </c>
       <c r="D45">
-        <v>-0.3495091045610709</v>
+        <v>-0.3048487467632724</v>
       </c>
       <c r="E45">
-        <v>0.04021946146483846</v>
+        <v>0.08138443042570703</v>
       </c>
       <c r="F45">
-        <v>-1.558972771483655</v>
+        <v>-1.137340779737238</v>
       </c>
       <c r="G45">
-        <v>0.1195963628028239</v>
+        <v>0.2560600881292628</v>
       </c>
       <c r="H45">
-        <v>0.6577528921060141</v>
+        <v>0.6496343645465574</v>
       </c>
       <c r="I45" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J45">
-        <v>0.1431885269192892</v>
+        <v>0.6864068815646385</v>
       </c>
       <c r="K45">
-        <v>0.6204836166502532</v>
+        <v>0.7933054336160084</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46">
-        <v>0.1353864164847706</v>
+        <v>0.1106431233283341</v>
       </c>
       <c r="D46">
-        <v>-0.06638112612333097</v>
+        <v>-0.08939182393112828</v>
       </c>
       <c r="E46">
-        <v>0.3371539590928723</v>
+        <v>0.3106780705877965</v>
       </c>
       <c r="F46">
-        <v>1.318132841412481</v>
+        <v>1.087302923091462</v>
       </c>
       <c r="G46">
-        <v>0.1880253725415308</v>
+        <v>0.2775417372379551</v>
       </c>
       <c r="H46">
-        <v>0.5115858867864171</v>
+        <v>0.5550834744759102</v>
       </c>
       <c r="I46" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J46">
-        <v>0.07164822060676942</v>
+        <v>0.4859654648622761</v>
       </c>
       <c r="K46">
-        <v>0.4657134339440013</v>
+        <v>0.7637718376832046</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
         <v>112</v>
       </c>
       <c r="C47">
-        <v>0.1246064261224201</v>
+        <v>0.1386141921529357</v>
       </c>
       <c r="D47">
-        <v>-0.01346279248134677</v>
+        <v>0.001780117482796523</v>
       </c>
       <c r="E47">
-        <v>0.2626756447261871</v>
+        <v>0.2754482668230749</v>
       </c>
       <c r="F47">
-        <v>1.772878467000403</v>
+        <v>1.991340118299319</v>
       </c>
       <c r="G47">
-        <v>0.07681991060435124</v>
+        <v>0.04710662831186148</v>
       </c>
       <c r="H47">
-        <v>0.4993294189282831</v>
+        <v>0.2355331415593074</v>
       </c>
       <c r="I47" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J47">
-        <v>0.05028553805226755</v>
+        <v>0.01771558454727829</v>
       </c>
       <c r="K47">
-        <v>0.3268559973397391</v>
+        <v>0.08857792273639145</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s">
         <v>112</v>
       </c>
       <c r="C48">
-        <v>0.04100806714027062</v>
+        <v>0.07226511453300043</v>
       </c>
       <c r="D48">
-        <v>-0.09846409924766084</v>
+        <v>-0.06597513873513781</v>
       </c>
       <c r="E48">
-        <v>0.1804802335282021</v>
+        <v>0.2105053678011387</v>
       </c>
       <c r="F48">
-        <v>0.5775866481691302</v>
+        <v>1.02760493022196</v>
       </c>
       <c r="G48">
-        <v>0.5637871280000045</v>
+        <v>0.3047415588862817</v>
       </c>
       <c r="H48">
-        <v>0.66629387854546</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I48" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J48">
-        <v>0.2823976720932692</v>
+        <v>0.05687610642456232</v>
       </c>
       <c r="K48">
-        <v>0.36711697372125</v>
+        <v>0.2388021824670327</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B49" t="s">
         <v>112</v>
       </c>
       <c r="C49">
-        <v>-0.09359389766785156</v>
+        <v>-0.1165888073041164</v>
       </c>
       <c r="D49">
-        <v>-0.2350232196381845</v>
+        <v>-0.2567904601555347</v>
       </c>
       <c r="E49">
-        <v>0.04783542430248139</v>
+        <v>0.02361284554730195</v>
       </c>
       <c r="F49">
-        <v>-1.300000341610627</v>
+        <v>-1.634691222344274</v>
       </c>
       <c r="G49">
-        <v>0.1941627475452882</v>
+        <v>0.1028813060458824</v>
       </c>
       <c r="H49">
-        <v>0.3722880864949198</v>
+        <v>0.2201229639232566</v>
       </c>
       <c r="I49" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J49">
-        <v>0.6202814912884667</v>
+        <v>0.2572626050159647</v>
       </c>
       <c r="K49">
-        <v>0.8648600795345258</v>
+        <v>0.6431565125399117</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B50" t="s">
         <v>112</v>
       </c>
       <c r="C50">
-        <v>0.03521097139697707</v>
+        <v>0.01123359074350171</v>
       </c>
       <c r="D50">
-        <v>-0.1272090958256161</v>
+        <v>-0.1499879703114361</v>
       </c>
       <c r="E50">
-        <v>0.1976310386195703</v>
+        <v>0.1724551517984395</v>
       </c>
       <c r="F50">
-        <v>0.4258667297506748</v>
+        <v>0.1369706386008993</v>
       </c>
       <c r="G50">
-        <v>0.6703768723069659</v>
+        <v>0.8911212371245572</v>
       </c>
       <c r="H50">
-        <v>0.8714899339990556</v>
+        <v>0.9899973285470545</v>
       </c>
       <c r="I50" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J50">
-        <v>0.9549330940863852</v>
+        <v>0.7573037881340388</v>
       </c>
       <c r="K50">
-        <v>0.9549330940863852</v>
+        <v>0.7573037881340388</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B51" t="s">
         <v>112</v>
       </c>
       <c r="C51">
-        <v>-0.09962827548578583</v>
+        <v>-0.09617395333887975</v>
       </c>
       <c r="D51">
-        <v>-0.2422019111403176</v>
+        <v>-0.2391574428287416</v>
       </c>
       <c r="E51">
-        <v>0.04294536016874591</v>
+        <v>0.04680953615098214</v>
       </c>
       <c r="F51">
-        <v>-1.372709947209598</v>
+        <v>-1.322219572255846</v>
       </c>
       <c r="G51">
-        <v>0.1704198291111124</v>
+        <v>0.1868321898741374</v>
       </c>
       <c r="H51">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I51" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J51">
-        <v>0.1585872698554967</v>
+        <v>0.2335510170276555</v>
       </c>
       <c r="K51">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
         <v>112</v>
       </c>
       <c r="C52">
-        <v>-0.0160299165036363</v>
+        <v>-0.02982487571894447</v>
       </c>
       <c r="D52">
-        <v>-0.1597675138389825</v>
+        <v>-0.1739613801093727</v>
       </c>
       <c r="E52">
-        <v>0.1277076808317099</v>
+        <v>0.1143116286714838</v>
       </c>
       <c r="F52">
-        <v>-0.2190767407781894</v>
+        <v>-0.4067585233410543</v>
       </c>
       <c r="G52">
-        <v>0.826674133818913</v>
+        <v>0.6843976026141663</v>
       </c>
       <c r="H52">
-        <v>0.9014071609929997</v>
+        <v>0.760441780682407</v>
       </c>
       <c r="I52" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J52">
-        <v>0.5515544725552879</v>
+        <v>0.4438616929368462</v>
       </c>
       <c r="K52">
-        <v>0.9212483962173839</v>
+        <v>0.7948008767625794</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B53" t="s">
         <v>112</v>
       </c>
       <c r="C53">
-        <v>-0.1448347855684649</v>
+        <v>-0.1576472737665626</v>
       </c>
       <c r="D53">
-        <v>-0.2908854340581543</v>
+        <v>-0.3040754083130183</v>
       </c>
       <c r="E53">
-        <v>0.001215862921224387</v>
+        <v>-0.01121913922010689</v>
       </c>
       <c r="F53">
-        <v>-1.948071008536221</v>
+        <v>-2.116381418731899</v>
       </c>
       <c r="G53">
-        <v>0.05193098976526055</v>
+        <v>0.03491439701797524</v>
       </c>
       <c r="H53">
-        <v>0.2250342889827957</v>
+        <v>0.1745719850898762</v>
       </c>
       <c r="I53" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J53">
-        <v>0.2923269202731353</v>
+        <v>0.1530632619248373</v>
       </c>
       <c r="K53">
-        <v>0.7232682404227637</v>
+        <v>0.6196861818806692</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B54" t="s">
         <v>112</v>
       </c>
       <c r="C54">
-        <v>0.08359835898214953</v>
+        <v>0.06634907761993529</v>
       </c>
       <c r="D54">
-        <v>-0.1112659240308052</v>
+        <v>-0.1267675109745545</v>
       </c>
       <c r="E54">
-        <v>0.2784626419951042</v>
+        <v>0.259465666214425</v>
       </c>
       <c r="F54">
-        <v>0.8427541516696501</v>
+        <v>0.6753786278889509</v>
       </c>
       <c r="G54">
-        <v>0.3997439661068986</v>
+        <v>0.4998159562061408</v>
       </c>
       <c r="H54">
-        <v>0.6577528921060141</v>
+        <v>0.6496343645465574</v>
       </c>
       <c r="I54" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J54">
-        <v>0.5075380573585024</v>
+        <v>0.7236716765226061</v>
       </c>
       <c r="K54">
-        <v>0.868457651346254</v>
+        <v>0.7933054336160084</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B55" t="s">
         <v>112</v>
       </c>
       <c r="C55">
-        <v>-0.1288048690648286</v>
+        <v>-0.1278223980476181</v>
       </c>
       <c r="D55">
-        <v>-0.3305724116729303</v>
+        <v>-0.3278573453070805</v>
       </c>
       <c r="E55">
-        <v>0.07296267354327299</v>
+        <v>0.07221254921184422</v>
       </c>
       <c r="F55">
-        <v>-1.254054376033238</v>
+        <v>-1.256125666493585</v>
       </c>
       <c r="G55">
-        <v>0.2103719539301528</v>
+        <v>0.2097856947092162</v>
       </c>
       <c r="H55">
-        <v>0.5115858867864171</v>
+        <v>0.5267102917345029</v>
       </c>
       <c r="I55" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J55">
-        <v>0.6943895671342932</v>
+        <v>0.5683204035928819</v>
       </c>
       <c r="K55">
-        <v>0.8068623218637324</v>
+        <v>0.7637718376832046</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s">
         <v>115</v>
       </c>
       <c r="C56">
-        <v>-0.07992492097307445</v>
+        <v>-0.0791587932562678</v>
       </c>
       <c r="D56">
-        <v>-0.2179941395768414</v>
+        <v>-0.215992867926407</v>
       </c>
       <c r="E56">
-        <v>0.05814429763069247</v>
+        <v>0.05767528141387139</v>
       </c>
       <c r="F56">
-        <v>-1.137157815847006</v>
+        <v>-1.137200154465057</v>
       </c>
       <c r="G56">
-        <v>0.255983276125734</v>
+        <v>0.2561187886509198</v>
       </c>
       <c r="H56">
-        <v>0.6655565179269085</v>
+        <v>0.6128744162107708</v>
       </c>
       <c r="I56" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J56">
-        <v>0.2301996775761501</v>
+        <v>0.3110000524549118</v>
       </c>
       <c r="K56">
-        <v>0.4987659680816585</v>
+        <v>0.6045735119489917</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B57" t="s">
         <v>115</v>
       </c>
       <c r="C57">
-        <v>0.01500158312447176</v>
+        <v>0.01996767448945858</v>
       </c>
       <c r="D57">
-        <v>-0.1244705832634597</v>
+        <v>-0.1182725787786797</v>
       </c>
       <c r="E57">
-        <v>0.1544737495124032</v>
+        <v>0.1582079277575968</v>
       </c>
       <c r="F57">
-        <v>0.2112929166950503</v>
+        <v>0.2839389501149243</v>
       </c>
       <c r="G57">
-        <v>0.8327394717111269</v>
+        <v>0.7766004996967484</v>
       </c>
       <c r="H57">
-        <v>0.8327394717111269</v>
+        <v>0.7766004996967484</v>
       </c>
       <c r="I57" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J57">
-        <v>0.7207646297154944</v>
+        <v>0.9151206559396106</v>
       </c>
       <c r="K57">
-        <v>0.7207646297154944</v>
+        <v>0.9151206559396106</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B58" t="s">
         <v>115</v>
       </c>
       <c r="C58">
-        <v>0.03962263702787698</v>
+        <v>0.03409316446551779</v>
       </c>
       <c r="D58">
-        <v>-0.101806684942456</v>
+        <v>-0.1061084883859006</v>
       </c>
       <c r="E58">
-        <v>0.1810519589982099</v>
+        <v>0.1742948173169361</v>
       </c>
       <c r="F58">
-        <v>0.5503504283425825</v>
+        <v>0.4780201288820792</v>
       </c>
       <c r="G58">
-        <v>0.582309608256282</v>
+        <v>0.6328906428926011</v>
       </c>
       <c r="H58">
-        <v>0.6965264869354365</v>
+        <v>0.6636118735888674</v>
       </c>
       <c r="I58" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J58">
-        <v>0.4132819510510046</v>
+        <v>0.4824473672388027</v>
       </c>
       <c r="K58">
-        <v>0.7675236233804372</v>
+        <v>0.6892105246268609</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B59" t="s">
         <v>115</v>
       </c>
       <c r="C59">
-        <v>0.04404713114605888</v>
+        <v>0.03793043288861654</v>
       </c>
       <c r="D59">
-        <v>-0.1183729360765343</v>
+        <v>-0.1232911281663212</v>
       </c>
       <c r="E59">
-        <v>0.2064671983686521</v>
+        <v>0.1991519939435543</v>
       </c>
       <c r="F59">
-        <v>0.5327375801305388</v>
+        <v>0.4624839673964193</v>
       </c>
       <c r="G59">
-        <v>0.5944372763283818</v>
+        <v>0.6439796367395463</v>
       </c>
       <c r="H59">
-        <v>0.8714899339990556</v>
+        <v>0.8049745459244328</v>
       </c>
       <c r="I59" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J59">
-        <v>0.5436420883650871</v>
+        <v>0.6808776104883645</v>
       </c>
       <c r="K59">
-        <v>0.7580233653467702</v>
+        <v>0.756530678320405</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s">
         <v>115</v>
       </c>
       <c r="C60">
-        <v>0.03530610787320053</v>
+        <v>0.03341664553556577</v>
       </c>
       <c r="D60">
-        <v>-0.1072675277813312</v>
+        <v>-0.1095668439542961</v>
       </c>
       <c r="E60">
-        <v>0.1778797435277323</v>
+        <v>0.1764001350254277</v>
       </c>
       <c r="F60">
-        <v>0.4864587411403308</v>
+        <v>0.4594190134887479</v>
       </c>
       <c r="G60">
-        <v>0.6268419062297526</v>
+        <v>0.6461767875715487</v>
       </c>
       <c r="H60">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I60" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J60">
-        <v>0.8754980415857079</v>
+        <v>0.9129517867579126</v>
       </c>
       <c r="K60">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
         <v>115</v>
       </c>
       <c r="C61">
-        <v>-0.05962039622434568</v>
+        <v>-0.06570982221016061</v>
       </c>
       <c r="D61">
-        <v>-0.2033579935596918</v>
+        <v>-0.2098463266005889</v>
       </c>
       <c r="E61">
-        <v>0.08411720111100049</v>
+        <v>0.07842668218026766</v>
       </c>
       <c r="F61">
-        <v>-0.814816601556908</v>
+        <v>-0.8961656874308704</v>
       </c>
       <c r="G61">
-        <v>0.4155412140696841</v>
+        <v>0.370690137497097</v>
       </c>
       <c r="H61">
-        <v>0.6752544728632367</v>
+        <v>0.6178168958284951</v>
       </c>
       <c r="I61" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J61">
-        <v>0.525962961001203</v>
+        <v>0.458777031402347</v>
       </c>
       <c r="K61">
-        <v>0.9212483962173839</v>
+        <v>0.7948008767625794</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
         <v>115</v>
       </c>
       <c r="C62">
-        <v>-0.06404489034252758</v>
+        <v>-0.06954709063325937</v>
       </c>
       <c r="D62">
-        <v>-0.2100955388322169</v>
+        <v>-0.215975225179715</v>
       </c>
       <c r="E62">
-        <v>0.08200575814716174</v>
+        <v>0.07688104391319631</v>
       </c>
       <c r="F62">
-        <v>-0.8614228524692509</v>
+        <v>-0.9336550314282218</v>
       </c>
       <c r="G62">
-        <v>0.3893925531823983</v>
+        <v>0.3510313833051265</v>
       </c>
       <c r="H62">
-        <v>0.685575246793741</v>
+        <v>0.6776626906689659</v>
       </c>
       <c r="I62" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J62">
-        <v>0.6534986315780325</v>
+        <v>0.6390527044142684</v>
       </c>
       <c r="K62">
-        <v>0.8716469215599764</v>
+        <v>0.7100585604602982</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
         <v>115</v>
       </c>
       <c r="C63">
-        <v>-0.09492650409754622</v>
+        <v>-0.09912646774572638</v>
       </c>
       <c r="D63">
-        <v>-0.2897907871105009</v>
+        <v>-0.2922430563402161</v>
       </c>
       <c r="E63">
-        <v>0.09993777891540848</v>
+        <v>0.09399012084876336</v>
       </c>
       <c r="F63">
-        <v>-0.9569530599132358</v>
+        <v>-1.009025297338449</v>
       </c>
       <c r="G63">
-        <v>0.3390247905892206</v>
+        <v>0.3135576113537648</v>
       </c>
       <c r="H63">
-        <v>0.6577528921060141</v>
+        <v>0.6496343645465574</v>
       </c>
       <c r="I63" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J63">
-        <v>0.5406624210777279</v>
+        <v>0.5083565467737732</v>
       </c>
       <c r="K63">
-        <v>0.868457651346254</v>
+        <v>0.7933054336160084</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s">
         <v>115</v>
       </c>
       <c r="C64">
-        <v>-0.004424494118181896</v>
+        <v>-0.003837268423098755</v>
       </c>
       <c r="D64">
-        <v>-0.2061920367262835</v>
+        <v>-0.2038722156825611</v>
       </c>
       <c r="E64">
-        <v>0.1973430484899197</v>
+        <v>0.1961976788363636</v>
       </c>
       <c r="F64">
-        <v>-0.04307722410592019</v>
+        <v>-0.03770928592408404</v>
       </c>
       <c r="G64">
-        <v>0.9656561074310929</v>
+        <v>0.9699378257101363</v>
       </c>
       <c r="H64">
-        <v>0.9950442841587558</v>
+        <v>0.9699378257101363</v>
       </c>
       <c r="I64" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J64">
-        <v>0.9089543158269823</v>
+        <v>0.8574624431116594</v>
       </c>
       <c r="K64">
-        <v>0.9089543158269823</v>
+        <v>0.9487069974091134</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s">
         <v>118</v>
       </c>
       <c r="C65">
-        <v>-0.05143723537237259</v>
+        <v>-0.04797839679947617</v>
       </c>
       <c r="D65">
-        <v>-0.1895064539761395</v>
+        <v>-0.1848124714696154</v>
       </c>
       <c r="E65">
-        <v>0.08663198323139433</v>
+        <v>0.08885567787066304</v>
       </c>
       <c r="F65">
-        <v>-0.7318400008047646</v>
+        <v>-0.6892606368406199</v>
       </c>
       <c r="G65">
-        <v>0.464587880084845</v>
+        <v>0.4910491471922609</v>
       </c>
       <c r="H65">
-        <v>0.7549553051378731</v>
+        <v>0.6765360331406861</v>
       </c>
       <c r="I65" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J65">
-        <v>0.4955479630617171</v>
+        <v>0.4387109552382666</v>
       </c>
       <c r="K65">
-        <v>0.6586654984750427</v>
+        <v>0.6045735119489917</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B66" t="s">
         <v>118</v>
       </c>
       <c r="C66">
-        <v>0.04453265271303526</v>
+        <v>0.02431596255068052</v>
       </c>
       <c r="D66">
-        <v>-0.09493951367489618</v>
+        <v>-0.1139242907174577</v>
       </c>
       <c r="E66">
-        <v>0.1840048191009667</v>
+        <v>0.1625562158188188</v>
       </c>
       <c r="F66">
-        <v>0.6272294065121407</v>
+        <v>0.3457713055828792</v>
       </c>
       <c r="G66">
-        <v>0.530777458559565</v>
+        <v>0.7296919384483573</v>
       </c>
       <c r="H66">
-        <v>0.66629387854546</v>
+        <v>0.7766004996967484</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J66">
-        <v>0.1284720063427783</v>
+        <v>0.178674646369412</v>
       </c>
       <c r="K66">
-        <v>0.2537209612578259</v>
+        <v>0.2977910772823533</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B67" t="s">
         <v>118</v>
       </c>
       <c r="C67">
-        <v>-0.1299779945958299</v>
+        <v>-0.149215661496998</v>
       </c>
       <c r="D67">
-        <v>-0.2714073165661628</v>
+        <v>-0.2894173143484163</v>
       </c>
       <c r="E67">
-        <v>0.01145132737450305</v>
+        <v>-0.009014008645579608</v>
       </c>
       <c r="F67">
-        <v>-1.805368101840285</v>
+        <v>-2.092152220488706</v>
       </c>
       <c r="G67">
-        <v>0.07158123387209249</v>
+        <v>0.03703939234656334</v>
       </c>
       <c r="H67">
-        <v>0.2123026769950926</v>
+        <v>0.2201229639232566</v>
       </c>
       <c r="I67" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J67">
-        <v>0.05959770319968507</v>
+        <v>0.03335818562426815</v>
       </c>
       <c r="K67">
-        <v>0.1665219219426752</v>
+        <v>0.182915392924374</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
         <v>118</v>
       </c>
       <c r="C68">
-        <v>-0.1094144888001272</v>
+        <v>-0.08453870673108693</v>
       </c>
       <c r="D68">
-        <v>-0.2718345560227204</v>
+        <v>-0.2457602677860247</v>
       </c>
       <c r="E68">
-        <v>0.05300557842246595</v>
+        <v>0.07668285432385083</v>
       </c>
       <c r="F68">
-        <v>-1.323337263471589</v>
+        <v>-1.03077643754731</v>
       </c>
       <c r="G68">
-        <v>0.1862906127387056</v>
+        <v>0.3032533370159061</v>
       </c>
       <c r="H68">
-        <v>0.85010061097029</v>
+        <v>0.7176670345313296</v>
       </c>
       <c r="I68" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J68">
-        <v>0.008220546141137468</v>
+        <v>0.009943088486260849</v>
       </c>
       <c r="K68">
-        <v>0.04266466093317318</v>
+        <v>0.03314362828753616</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B69" t="s">
         <v>118</v>
       </c>
       <c r="C69">
-        <v>0.002470531310701581</v>
+        <v>0.00193346613299885</v>
       </c>
       <c r="D69">
-        <v>-0.1401031043438302</v>
+        <v>-0.141050023356863</v>
       </c>
       <c r="E69">
-        <v>0.1450441669652333</v>
+        <v>0.1449169556228607</v>
       </c>
       <c r="F69">
-        <v>0.03403976319530565</v>
+        <v>0.02658169571481486</v>
       </c>
       <c r="G69">
-        <v>0.9728581861110144</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="H69">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I69" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J69">
-        <v>0.4966109064596747</v>
+        <v>0.4745848295497084</v>
       </c>
       <c r="K69">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
         <v>118</v>
       </c>
       <c r="C70">
-        <v>-0.09349935677470628</v>
+        <v>-0.07036089321715784</v>
       </c>
       <c r="D70">
-        <v>-0.2372369541100524</v>
+        <v>-0.2144973976075861</v>
       </c>
       <c r="E70">
-        <v>0.05023824056063989</v>
+        <v>0.07377561117327043</v>
       </c>
       <c r="F70">
-        <v>-1.277831630776941</v>
+        <v>-0.9595980649062572</v>
       </c>
       <c r="G70">
-        <v>0.2018650453257872</v>
+        <v>0.337823080722045</v>
       </c>
       <c r="H70">
-        <v>0.5867252102342169</v>
+        <v>0.6178168958284951</v>
       </c>
       <c r="I70" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J70">
-        <v>0.1757831074967802</v>
+        <v>0.2139663810382114</v>
       </c>
       <c r="K70">
-        <v>0.761726799152714</v>
+        <v>0.7132212701273715</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
         <v>118</v>
       </c>
       <c r="C71">
-        <v>-0.1140628625704089</v>
+        <v>-0.1350378479830689</v>
       </c>
       <c r="D71">
-        <v>-0.2601135110600982</v>
+        <v>-0.2814659825295246</v>
       </c>
       <c r="E71">
-        <v>0.03198778591928042</v>
+        <v>0.01139028656338678</v>
       </c>
       <c r="F71">
-        <v>-1.534179478030347</v>
+        <v>-1.812854643589321</v>
       </c>
       <c r="G71">
-        <v>0.1255788491339026</v>
+        <v>0.07058543288459021</v>
       </c>
       <c r="H71">
-        <v>0.3357065321651216</v>
+        <v>0.2352847762819674</v>
       </c>
       <c r="I71" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J71">
-        <v>0.7375473951661338</v>
+        <v>0.5956352941163663</v>
       </c>
       <c r="K71">
-        <v>0.8716469215599764</v>
+        <v>0.7100585604602982</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B72" t="s">
         <v>118</v>
       </c>
       <c r="C72">
-        <v>-0.09596988808540785</v>
+        <v>-0.07229435935015668</v>
       </c>
       <c r="D72">
-        <v>-0.2908341710983625</v>
+        <v>-0.2654109479446464</v>
       </c>
       <c r="E72">
-        <v>0.09889439492754684</v>
+        <v>0.1208222292443331</v>
       </c>
       <c r="F72">
-        <v>-0.9674714025967779</v>
+        <v>-0.7358966691550397</v>
       </c>
       <c r="G72">
-        <v>0.3337472110628484</v>
+        <v>0.4622143744215789</v>
       </c>
       <c r="H72">
-        <v>0.6577528921060141</v>
+        <v>0.6496343645465574</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J72">
-        <v>0.1143564586932039</v>
+        <v>0.1287573469366913</v>
       </c>
       <c r="K72">
-        <v>0.6204836166502532</v>
+        <v>0.4687014332580133</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
         <v>118</v>
       </c>
       <c r="C73">
-        <v>-0.02056350579570265</v>
+        <v>-0.06467695476591104</v>
       </c>
       <c r="D73">
-        <v>-0.2223310484038043</v>
+        <v>-0.2647119020253734</v>
       </c>
       <c r="E73">
-        <v>0.181204036812399</v>
+        <v>0.1353579924935513</v>
       </c>
       <c r="F73">
-        <v>-0.2002079161829399</v>
+        <v>-0.6355880045517529</v>
       </c>
       <c r="G73">
-        <v>0.8413943410850161</v>
+        <v>0.5253995756108851</v>
       </c>
       <c r="H73">
-        <v>0.9950442841587558</v>
+        <v>0.6567494695136065</v>
       </c>
       <c r="I73" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J73">
-        <v>0.4425527619543425</v>
+        <v>0.6110174701465636</v>
       </c>
       <c r="K73">
-        <v>0.8068623218637324</v>
+        <v>0.7637718376832046</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B74" t="s">
         <v>121</v>
       </c>
       <c r="C74">
-        <v>0.04175886696737764</v>
+        <v>0.1389872600813363</v>
       </c>
       <c r="D74">
-        <v>-0.09631035163638928</v>
+        <v>0.002153185411197106</v>
       </c>
       <c r="E74">
-        <v>0.1798280855711445</v>
+        <v>0.2758213347514755</v>
       </c>
       <c r="F74">
-        <v>0.5941378655709439</v>
+        <v>1.996699635395918</v>
       </c>
       <c r="G74">
-        <v>0.5526719913822089</v>
+        <v>0.04651851099964628</v>
       </c>
       <c r="H74">
-        <v>0.7983039875520795</v>
+        <v>0.2355331415593074</v>
       </c>
       <c r="I74" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J74">
-        <v>0.1244614570086635</v>
+        <v>0.01334067206138983</v>
       </c>
       <c r="K74">
-        <v>0.4044997352781564</v>
+        <v>0.08857792273639145</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B75" t="s">
         <v>121</v>
       </c>
       <c r="C75">
-        <v>0.082592480183674</v>
+        <v>0.04618185999653664</v>
       </c>
       <c r="D75">
-        <v>-0.05687968620425744</v>
+        <v>-0.09205839327160159</v>
       </c>
       <c r="E75">
-        <v>0.2220646465716055</v>
+        <v>0.1844221132646749</v>
       </c>
       <c r="F75">
-        <v>1.163290960046667</v>
+        <v>0.6567028548413898</v>
       </c>
       <c r="G75">
-        <v>0.2452319907608884</v>
+        <v>0.5117404196009452</v>
       </c>
       <c r="H75">
-        <v>0.6008421903295255</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I75" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J75">
-        <v>0.06138773666665809</v>
+        <v>0.1445810156357069</v>
       </c>
       <c r="K75">
-        <v>0.1995101441666388</v>
+        <v>0.2923540735553978</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B76" t="s">
         <v>121</v>
       </c>
       <c r="C76">
-        <v>-0.001119433826108742</v>
+        <v>-0.114213467883197</v>
       </c>
       <c r="D76">
-        <v>-0.1425487557964417</v>
+        <v>-0.2544151207346154</v>
       </c>
       <c r="E76">
-        <v>0.1403098881442242</v>
+        <v>0.02598818496822133</v>
       </c>
       <c r="F76">
-        <v>-0.01554870982632153</v>
+        <v>-1.601386597387122</v>
       </c>
       <c r="G76">
-        <v>0.9876002426778763</v>
+        <v>0.1100614819616283</v>
       </c>
       <c r="H76">
-        <v>0.9876002426778763</v>
+        <v>0.2201229639232566</v>
       </c>
       <c r="I76" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J76">
-        <v>0.7318046826830603</v>
+        <v>0.3906617329584844</v>
       </c>
       <c r="K76">
-        <v>0.8648600795345258</v>
+        <v>0.6511028882641406</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B77" t="s">
         <v>121</v>
       </c>
       <c r="C77">
-        <v>-0.01481007177132974</v>
+        <v>0.08012042063372338</v>
       </c>
       <c r="D77">
-        <v>-0.1772301389939229</v>
+        <v>-0.08110114042121438</v>
       </c>
       <c r="E77">
-        <v>0.1476099954512635</v>
+        <v>0.2413419816886611</v>
       </c>
       <c r="F77">
-        <v>-0.1791236248929633</v>
+        <v>0.9769044849281138</v>
       </c>
       <c r="G77">
-        <v>0.8579087010624695</v>
+        <v>0.3291924848302668</v>
       </c>
       <c r="H77">
-        <v>0.992255362689753</v>
+        <v>0.7176670345313296</v>
       </c>
       <c r="I77" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J77">
-        <v>0.3033577800106258</v>
+        <v>0.4944349142900637</v>
       </c>
       <c r="K77">
-        <v>0.6572751900230225</v>
+        <v>0.7063355918429481</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B78" t="s">
         <v>121</v>
       </c>
       <c r="C78">
-        <v>-0.03261499552604649</v>
+        <v>-0.06003624873533071</v>
       </c>
       <c r="D78">
-        <v>-0.1751886311805782</v>
+        <v>-0.2030197382251926</v>
       </c>
       <c r="E78">
-        <v>0.1099586401284852</v>
+        <v>0.08294724075453118</v>
       </c>
       <c r="F78">
-        <v>-0.4493797425329128</v>
+        <v>-0.8253908710913267</v>
       </c>
       <c r="G78">
-        <v>0.6533404165355055</v>
+        <v>0.4096297020788422</v>
       </c>
       <c r="H78">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I78" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J78">
-        <v>0.9395313521223855</v>
+        <v>0.7732325951306767</v>
       </c>
       <c r="K78">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B79" t="s">
         <v>121</v>
       </c>
       <c r="C79">
-        <v>-0.07344860874234285</v>
+        <v>0.03276915134946894</v>
       </c>
       <c r="D79">
-        <v>-0.217186206077689</v>
+        <v>-0.1113673530409593</v>
       </c>
       <c r="E79">
-        <v>0.07028898859300331</v>
+        <v>0.1769056557398972</v>
       </c>
       <c r="F79">
-        <v>-1.003803220953445</v>
+        <v>0.4469132324190363</v>
       </c>
       <c r="G79">
-        <v>0.315928959356886</v>
+        <v>0.6551736895984315</v>
       </c>
       <c r="H79">
-        <v>0.5867252102342169</v>
+        <v>0.760441780682407</v>
       </c>
       <c r="I79" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J79">
-        <v>0.6831133375951312</v>
+        <v>0.4768805260575476</v>
       </c>
       <c r="K79">
-        <v>0.9212483962173839</v>
+        <v>0.7948008767625794</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
         <v>121</v>
       </c>
       <c r="C80">
-        <v>-0.05975797079712185</v>
+        <v>-0.1615647371674515</v>
       </c>
       <c r="D80">
-        <v>-0.2058086192868112</v>
+        <v>-0.3079928717139072</v>
       </c>
       <c r="E80">
-        <v>0.08629267769256747</v>
+        <v>-0.01513660262099581</v>
       </c>
       <c r="F80">
-        <v>-0.8037625076180172</v>
+        <v>-2.168972539099006</v>
       </c>
       <c r="G80">
-        <v>0.4218924595653791</v>
+        <v>0.03065890032230952</v>
       </c>
       <c r="H80">
-        <v>0.685575246793741</v>
+        <v>0.1745719850898762</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J80">
-        <v>0.7374420500046679</v>
+        <v>0.4337803273164684</v>
       </c>
       <c r="K80">
-        <v>0.8716469215599764</v>
+        <v>0.6196861818806692</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B81" t="s">
         <v>121</v>
       </c>
       <c r="C81">
-        <v>-0.04083361321629636</v>
+        <v>0.09280540008479965</v>
       </c>
       <c r="D81">
-        <v>-0.2356978962292511</v>
+        <v>-0.1003111885096901</v>
       </c>
       <c r="E81">
-        <v>0.1540306697966583</v>
+        <v>0.2859219886792894</v>
       </c>
       <c r="F81">
-        <v>-0.4116432126742401</v>
+        <v>0.9446820667047918</v>
       </c>
       <c r="G81">
-        <v>0.680766432372839</v>
+        <v>0.3453775784170754</v>
       </c>
       <c r="H81">
-        <v>0.8736494904824352</v>
+        <v>0.6496343645465574</v>
       </c>
       <c r="I81" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J81">
-        <v>0.8121861695802933</v>
+        <v>0.4310191577405731</v>
       </c>
       <c r="K81">
-        <v>0.8798683503786511</v>
+        <v>0.7933054336160084</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B82" t="s">
         <v>121</v>
       </c>
       <c r="C82">
-        <v>0.013690637945221</v>
+        <v>-0.1943338885169204</v>
       </c>
       <c r="D82">
-        <v>-0.1880769046628806</v>
+        <v>-0.3943688357763828</v>
       </c>
       <c r="E82">
-        <v>0.2154581805533226</v>
+        <v>0.005701058742541953</v>
       </c>
       <c r="F82">
-        <v>0.1332931320884297</v>
+        <v>-1.909741868124461</v>
       </c>
       <c r="G82">
-        <v>0.8940118681562268</v>
+        <v>0.05686402499655289</v>
       </c>
       <c r="H82">
-        <v>0.9950442841587558</v>
+        <v>0.5097729523195305</v>
       </c>
       <c r="I82" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J82">
-        <v>0.5773355411997998</v>
+        <v>0.2549944440814035</v>
       </c>
       <c r="K82">
-        <v>0.8068623218637324</v>
+        <v>0.7637718376832046</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B83" t="s">
         <v>124</v>
       </c>
       <c r="C83">
-        <v>0.06292735703715739</v>
+        <v>0.06439184914287746</v>
       </c>
       <c r="D83">
-        <v>-0.07514186156660953</v>
+        <v>-0.07244222552726173</v>
       </c>
       <c r="E83">
-        <v>0.2009965756409243</v>
+        <v>0.2012259238130167</v>
       </c>
       <c r="F83">
-        <v>0.8953194449764369</v>
+        <v>0.9250573155468468</v>
       </c>
       <c r="G83">
-        <v>0.3710204925857702</v>
+        <v>0.3554802333740317</v>
       </c>
       <c r="H83">
-        <v>0.6890380576592875</v>
+        <v>0.6128744162107708</v>
       </c>
       <c r="I83" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J83">
-        <v>0.1982736258764735</v>
+        <v>0.2518442092842171</v>
       </c>
       <c r="K83">
-        <v>0.4987659680816585</v>
+        <v>0.6045735119489917</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B84" t="s">
         <v>124</v>
       </c>
       <c r="C84">
-        <v>0.04745717123430632</v>
+        <v>0.04263305599367222</v>
       </c>
       <c r="D84">
-        <v>-0.09201499515362513</v>
+        <v>-0.09560719727446601</v>
       </c>
       <c r="E84">
-        <v>0.1869293376222378</v>
+        <v>0.1808733092618105</v>
       </c>
       <c r="F84">
-        <v>0.6684203957004778</v>
+        <v>0.6062391073845227</v>
       </c>
       <c r="G84">
-        <v>0.5041546402369816</v>
+        <v>0.544691482492264</v>
       </c>
       <c r="H84">
-        <v>0.66629387854546</v>
+        <v>0.68086435311533</v>
       </c>
       <c r="I84" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J84">
-        <v>0.6456349497369116</v>
+        <v>0.7914239115006593</v>
       </c>
       <c r="K84">
-        <v>0.6994378622149875</v>
+        <v>0.8793599016673992</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B85" t="s">
         <v>124</v>
       </c>
       <c r="C85">
-        <v>0.1268905813232421</v>
+        <v>0.1243093510807597</v>
       </c>
       <c r="D85">
-        <v>-0.01453874064709085</v>
+        <v>-0.0158923017706587</v>
       </c>
       <c r="E85">
-        <v>0.268319903293575</v>
+        <v>0.264511003932178</v>
       </c>
       <c r="F85">
-        <v>1.762484554845576</v>
+        <v>1.742940937177387</v>
       </c>
       <c r="G85">
-        <v>0.07856056224023915</v>
+        <v>0.08209362235677765</v>
       </c>
       <c r="H85">
-        <v>0.2123026769950926</v>
+        <v>0.2201229639232566</v>
       </c>
       <c r="I85" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J85">
-        <v>0.03499697596408941</v>
+        <v>0.05487461787731219</v>
       </c>
       <c r="K85">
-        <v>0.1665219219426752</v>
+        <v>0.182915392924374</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B86" t="s">
         <v>124</v>
       </c>
       <c r="C86">
-        <v>0.06617015276934031</v>
+        <v>0.05506161956194638</v>
       </c>
       <c r="D86">
-        <v>-0.09624991445325289</v>
+        <v>-0.1061599414929914</v>
       </c>
       <c r="E86">
-        <v>0.2285902199919335</v>
+        <v>0.2162831806168841</v>
       </c>
       <c r="F86">
-        <v>0.8003092629645767</v>
+        <v>0.6713637131709008</v>
       </c>
       <c r="G86">
-        <v>0.4238881972972374</v>
+        <v>0.5023669241719307</v>
       </c>
       <c r="H86">
-        <v>0.8714899339990556</v>
+        <v>0.7176670345313296</v>
       </c>
       <c r="I86" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J86">
-        <v>0.4214029297970086</v>
+        <v>0.4622676271543358</v>
       </c>
       <c r="K86">
-        <v>0.6847797609201389</v>
+        <v>0.7063355918429481</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
         <v>124</v>
       </c>
       <c r="C87">
-        <v>-0.03099354888393316</v>
+        <v>-0.02912463325550486</v>
       </c>
       <c r="D87">
-        <v>-0.1735671845384649</v>
+        <v>-0.1721081227453667</v>
       </c>
       <c r="E87">
-        <v>0.1115800867705986</v>
+        <v>0.113858856234357</v>
       </c>
       <c r="F87">
-        <v>-0.4270389369368536</v>
+        <v>-0.4004115333546774</v>
       </c>
       <c r="G87">
-        <v>0.6695234135498888</v>
+        <v>0.6890619844187288</v>
       </c>
       <c r="H87">
-        <v>0.9919088267494406</v>
+        <v>0.9788063058063374</v>
       </c>
       <c r="I87" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J87">
-        <v>0.4701035807203231</v>
+        <v>0.4767184657100512</v>
       </c>
       <c r="K87">
-        <v>0.9395313521223855</v>
+        <v>0.9694454941851673</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B88" t="s">
         <v>124</v>
       </c>
       <c r="C88">
-        <v>-0.01552336308108209</v>
+        <v>-0.007365840106299619</v>
       </c>
       <c r="D88">
-        <v>-0.1592609604164283</v>
+        <v>-0.1515023444967279</v>
       </c>
       <c r="E88">
-        <v>0.1282142342542641</v>
+        <v>0.1367706642841287</v>
       </c>
       <c r="F88">
-        <v>-0.2121538056014504</v>
+        <v>-0.1004570236281535</v>
       </c>
       <c r="G88">
-        <v>0.8320681486089229</v>
+        <v>0.9200306038321762</v>
       </c>
       <c r="H88">
-        <v>0.9014071609929997</v>
+        <v>0.9200306038321762</v>
       </c>
       <c r="I88" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J88">
-        <v>0.9587258105901777</v>
+        <v>0.9103015471467956</v>
       </c>
       <c r="K88">
-        <v>0.9587258105901777</v>
+        <v>0.9694208397924868</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B89" t="s">
         <v>124</v>
       </c>
       <c r="C89">
-        <v>0.04519706547281972</v>
+        <v>0.06188189141251365</v>
       </c>
       <c r="D89">
-        <v>-0.1008535830168696</v>
+        <v>-0.08454624313394202</v>
       </c>
       <c r="E89">
-        <v>0.191247713962509</v>
+        <v>0.2083100259589693</v>
       </c>
       <c r="F89">
-        <v>0.6079139936786297</v>
+        <v>0.8307513476912861</v>
       </c>
       <c r="G89">
-        <v>0.5435034505508869</v>
+        <v>0.4065976144013795</v>
       </c>
       <c r="H89">
-        <v>0.706554485716153</v>
+        <v>0.6776626906689659</v>
       </c>
       <c r="I89" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J89">
-        <v>0.2342865829095094</v>
+        <v>0.2578750906818356</v>
       </c>
       <c r="K89">
-        <v>0.7232682404227637</v>
+        <v>0.6196861818806692</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B90" t="s">
         <v>124</v>
       </c>
       <c r="C90">
-        <v>0.01547018580285107</v>
+        <v>0.02175879314920524</v>
       </c>
       <c r="D90">
-        <v>-0.1793940972101036</v>
+        <v>-0.1713577954452845</v>
       </c>
       <c r="E90">
-        <v>0.2103344688158058</v>
+        <v>0.214875381743695</v>
       </c>
       <c r="F90">
-        <v>0.1559547755624902</v>
+        <v>0.2214864831401114</v>
       </c>
       <c r="G90">
-        <v>0.8761277164826287</v>
+        <v>0.8248239288351114</v>
       </c>
       <c r="H90">
-        <v>0.8986522439534611</v>
+        <v>0.8248239288351114</v>
       </c>
       <c r="I90" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J90">
-        <v>0.5417777316524033</v>
+        <v>0.5167181371911933</v>
       </c>
       <c r="K90">
-        <v>0.868457651346254</v>
+        <v>0.7933054336160084</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B91" t="s">
         <v>124</v>
       </c>
       <c r="C91">
-        <v>0.06072042855390179</v>
+        <v>0.06924773151881328</v>
       </c>
       <c r="D91">
-        <v>-0.1410471140541998</v>
+        <v>-0.1307872157406491</v>
       </c>
       <c r="E91">
-        <v>0.2624879711620034</v>
+        <v>0.2692826787782756</v>
       </c>
       <c r="F91">
-        <v>0.5911788870676061</v>
+        <v>0.6805055626857648</v>
       </c>
       <c r="G91">
-        <v>0.5546511859026946</v>
+        <v>0.4965684997482148</v>
       </c>
       <c r="H91">
-        <v>0.8011628240816699</v>
+        <v>0.6567494695136065</v>
       </c>
       <c r="I91" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J91">
-        <v>0.3743772245877102</v>
+        <v>0.423693585606351</v>
       </c>
       <c r="K91">
-        <v>0.8068623218637324</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" t="s">
-        <v>136</v>
-      </c>
-      <c r="B92" t="s">
-        <v>127</v>
-      </c>
-      <c r="C92">
-        <v>0.005722230423452756</v>
-      </c>
-      <c r="D92">
-        <v>-0.1323469881803142</v>
-      </c>
-      <c r="E92">
-        <v>0.1437914490272197</v>
-      </c>
-      <c r="F92">
-        <v>0.08141489501502244</v>
-      </c>
-      <c r="G92">
-        <v>0.9351425660822107</v>
-      </c>
-      <c r="H92">
-        <v>0.9442169441935748</v>
-      </c>
-      <c r="I92" t="s">
-        <v>137</v>
-      </c>
-      <c r="J92">
-        <v>0.6721321179217384</v>
-      </c>
-      <c r="K92">
-        <v>0.7281431277485499</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" t="s">
-        <v>138</v>
-      </c>
-      <c r="B93" t="s">
-        <v>127</v>
-      </c>
-      <c r="C93">
-        <v>0.01836233966793953</v>
-      </c>
-      <c r="D93">
-        <v>-0.1211098267199919</v>
-      </c>
-      <c r="E93">
-        <v>0.157834506055871</v>
-      </c>
-      <c r="F93">
-        <v>0.2586281910110592</v>
-      </c>
-      <c r="G93">
-        <v>0.7960219724011264</v>
-      </c>
-      <c r="H93">
-        <v>0.8327394717111269</v>
-      </c>
-      <c r="I93" t="s">
-        <v>137</v>
-      </c>
-      <c r="J93">
-        <v>0.1311737213772686</v>
-      </c>
-      <c r="K93">
-        <v>0.2537209612578259</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" t="s">
-        <v>139</v>
-      </c>
-      <c r="B94" t="s">
-        <v>127</v>
-      </c>
-      <c r="C94">
-        <v>-0.1338865004243649</v>
-      </c>
-      <c r="D94">
-        <v>-0.2753158223946979</v>
-      </c>
-      <c r="E94">
-        <v>0.007542821545968054</v>
-      </c>
-      <c r="F94">
-        <v>-1.859656458655111</v>
-      </c>
-      <c r="G94">
-        <v>0.06348488157320516</v>
-      </c>
-      <c r="H94">
-        <v>0.2123026769950926</v>
-      </c>
-      <c r="I94" t="s">
-        <v>143</v>
-      </c>
-      <c r="J94">
-        <v>0.02475933622097209</v>
-      </c>
-      <c r="K94">
-        <v>0.1665219219426752</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" t="s">
-        <v>140</v>
-      </c>
-      <c r="B95" t="s">
-        <v>127</v>
-      </c>
-      <c r="C95">
-        <v>0.003839043198792115</v>
-      </c>
-      <c r="D95">
-        <v>-0.1585810240238011</v>
-      </c>
-      <c r="E95">
-        <v>0.1662591104213853</v>
-      </c>
-      <c r="F95">
-        <v>0.04643214053962536</v>
-      </c>
-      <c r="G95">
-        <v>0.9629832111610996</v>
-      </c>
-      <c r="H95">
-        <v>0.992255362689753</v>
-      </c>
-      <c r="I95" t="s">
-        <v>143</v>
-      </c>
-      <c r="J95">
-        <v>0.1266966761426336</v>
-      </c>
-      <c r="K95">
-        <v>0.3294113579708473</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" t="s">
-        <v>141</v>
-      </c>
-      <c r="B96" t="s">
-        <v>127</v>
-      </c>
-      <c r="C96">
-        <v>-0.008675344312603136</v>
-      </c>
-      <c r="D96">
-        <v>-0.1512489799671349</v>
-      </c>
-      <c r="E96">
-        <v>0.1338982913419286</v>
-      </c>
-      <c r="F96">
-        <v>-0.119531642752138</v>
-      </c>
-      <c r="G96">
-        <v>0.9048992117122685</v>
-      </c>
-      <c r="H96">
-        <v>0.9919088267494406</v>
-      </c>
-      <c r="I96" t="s">
-        <v>137</v>
-      </c>
-      <c r="J96">
-        <v>0.4245355897228325</v>
-      </c>
-      <c r="K96">
-        <v>0.9395313521223855</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11">
-      <c r="A97" t="s">
-        <v>142</v>
-      </c>
-      <c r="B97" t="s">
-        <v>127</v>
-      </c>
-      <c r="C97">
-        <v>-0.02131545355708991</v>
-      </c>
-      <c r="D97">
-        <v>-0.1650530508924361</v>
-      </c>
-      <c r="E97">
-        <v>0.1224221437782562</v>
-      </c>
-      <c r="F97">
-        <v>-0.291312814538792</v>
-      </c>
-      <c r="G97">
-        <v>0.7709254191854933</v>
-      </c>
-      <c r="H97">
-        <v>0.9014071609929997</v>
-      </c>
-      <c r="I97" t="s">
-        <v>143</v>
-      </c>
-      <c r="J97">
-        <v>0.8310924080618316</v>
-      </c>
-      <c r="K97">
-        <v>0.9587258105901777</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
-      <c r="A98" t="s">
-        <v>144</v>
-      </c>
-      <c r="B98" t="s">
-        <v>127</v>
-      </c>
-      <c r="C98">
-        <v>-0.1590409971802469</v>
-      </c>
-      <c r="D98">
-        <v>-0.3050916456699362</v>
-      </c>
-      <c r="E98">
-        <v>-0.0129903486905576</v>
-      </c>
-      <c r="F98">
-        <v>-2.139148786387874</v>
-      </c>
-      <c r="G98">
-        <v>0.03287730330910381</v>
-      </c>
-      <c r="H98">
-        <v>0.2250342889827957</v>
-      </c>
-      <c r="I98" t="s">
-        <v>143</v>
-      </c>
-      <c r="J98">
-        <v>0.44508814795247</v>
-      </c>
-      <c r="K98">
-        <v>0.7232682404227637</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" t="s">
-        <v>145</v>
-      </c>
-      <c r="B99" t="s">
-        <v>127</v>
-      </c>
-      <c r="C99">
-        <v>-0.01264010924448677</v>
-      </c>
-      <c r="D99">
-        <v>-0.2075043922574415</v>
-      </c>
-      <c r="E99">
-        <v>0.1822241737684679</v>
-      </c>
-      <c r="F99">
-        <v>-0.1274248044225814</v>
-      </c>
-      <c r="G99">
-        <v>0.8986522439534611</v>
-      </c>
-      <c r="H99">
-        <v>0.8986522439534611</v>
-      </c>
-      <c r="I99" t="s">
-        <v>143</v>
-      </c>
-      <c r="J99">
-        <v>0.428431941201159</v>
-      </c>
-      <c r="K99">
-        <v>0.868457651346254</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
-      <c r="A100" t="s">
-        <v>146</v>
-      </c>
-      <c r="B100" t="s">
-        <v>127</v>
-      </c>
-      <c r="C100">
-        <v>-0.137725543623157</v>
-      </c>
-      <c r="D100">
-        <v>-0.3394930862312586</v>
-      </c>
-      <c r="E100">
-        <v>0.06404199898494461</v>
-      </c>
-      <c r="F100">
-        <v>-1.340906767936292</v>
-      </c>
-      <c r="G100">
-        <v>0.1805218846952044</v>
-      </c>
-      <c r="H100">
-        <v>0.5115858867864171</v>
-      </c>
-      <c r="I100" t="s">
-        <v>143</v>
-      </c>
-      <c r="J100">
-        <v>0.6458234438657655</v>
-      </c>
-      <c r="K100">
-        <v>0.8068623218637324</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
-      <c r="A101" t="s">
-        <v>136</v>
-      </c>
-      <c r="B101" t="s">
-        <v>130</v>
-      </c>
-      <c r="C101">
-        <v>0.163086005765209</v>
-      </c>
-      <c r="D101">
-        <v>0.02501678716144212</v>
-      </c>
-      <c r="E101">
-        <v>0.301155224368976</v>
-      </c>
-      <c r="F101">
-        <v>2.320359205280343</v>
-      </c>
-      <c r="G101">
-        <v>0.02069808326065618</v>
-      </c>
-      <c r="H101">
-        <v>0.2690750823885304</v>
-      </c>
-      <c r="I101" t="s">
-        <v>137</v>
-      </c>
-      <c r="J101">
-        <v>0.005887560427965195</v>
-      </c>
-      <c r="K101">
-        <v>0.07653828556354753</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11">
-      <c r="A102" t="s">
-        <v>138</v>
-      </c>
-      <c r="B102" t="s">
-        <v>130</v>
-      </c>
-      <c r="C102">
-        <v>0.1126997874291381</v>
-      </c>
-      <c r="D102">
-        <v>-0.02677237895879331</v>
-      </c>
-      <c r="E102">
-        <v>0.2521719538170696</v>
-      </c>
-      <c r="F102">
-        <v>1.5873435889556</v>
-      </c>
-      <c r="G102">
-        <v>0.1130278697909898</v>
-      </c>
-      <c r="H102">
-        <v>0.6008421903295255</v>
-      </c>
-      <c r="I102" t="s">
-        <v>137</v>
-      </c>
-      <c r="J102">
-        <v>0.003748473858983131</v>
-      </c>
-      <c r="K102">
-        <v>0.0487301601667807</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
-      <c r="A103" t="s">
-        <v>139</v>
-      </c>
-      <c r="B103" t="s">
-        <v>130</v>
-      </c>
-      <c r="C103">
-        <v>-0.1340475556899034</v>
-      </c>
-      <c r="D103">
-        <v>-0.2754768776602363</v>
-      </c>
-      <c r="E103">
-        <v>0.007381766280429553</v>
-      </c>
-      <c r="F103">
-        <v>-1.861893483775715</v>
-      </c>
-      <c r="G103">
-        <v>0.06316824268166753</v>
-      </c>
-      <c r="H103">
-        <v>0.2123026769950926</v>
-      </c>
-      <c r="I103" t="s">
-        <v>143</v>
-      </c>
-      <c r="J103">
-        <v>0.06404689305487508</v>
-      </c>
-      <c r="K103">
-        <v>0.1665219219426752</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11">
-      <c r="A104" t="s">
-        <v>140</v>
-      </c>
-      <c r="B104" t="s">
-        <v>130</v>
-      </c>
-      <c r="C104">
-        <v>-0.0008029266225813708</v>
-      </c>
-      <c r="D104">
-        <v>-0.1632229938451746</v>
-      </c>
-      <c r="E104">
-        <v>0.1616171406000118</v>
-      </c>
-      <c r="F104">
-        <v>-0.009711170167200751</v>
-      </c>
-      <c r="G104">
-        <v>0.992255362689753</v>
-      </c>
-      <c r="H104">
-        <v>0.992255362689753</v>
-      </c>
-      <c r="I104" t="s">
-        <v>143</v>
-      </c>
-      <c r="J104">
-        <v>0.6940396467842804</v>
-      </c>
-      <c r="K104">
-        <v>0.8202286734723314</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
-      <c r="A105" t="s">
-        <v>141</v>
-      </c>
-      <c r="B105" t="s">
-        <v>130</v>
-      </c>
-      <c r="C105">
-        <v>-0.06810658877660083</v>
-      </c>
-      <c r="D105">
-        <v>-0.2106802244311326</v>
-      </c>
-      <c r="E105">
-        <v>0.0744670468779309</v>
-      </c>
-      <c r="F105">
-        <v>-0.938394159974113</v>
-      </c>
-      <c r="G105">
-        <v>0.3484669161957751</v>
-      </c>
-      <c r="H105">
-        <v>0.9919088267494406</v>
-      </c>
-      <c r="I105" t="s">
-        <v>143</v>
-      </c>
-      <c r="J105">
-        <v>0.7676014448680983</v>
-      </c>
-      <c r="K105">
-        <v>0.9395313521223855</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
-      <c r="A106" t="s">
-        <v>142</v>
-      </c>
-      <c r="B106" t="s">
-        <v>130</v>
-      </c>
-      <c r="C106">
-        <v>-0.01772037044052991</v>
-      </c>
-      <c r="D106">
-        <v>-0.1614579677758761</v>
-      </c>
-      <c r="E106">
-        <v>0.1260172268948163</v>
-      </c>
-      <c r="F106">
-        <v>-0.2421797394024369</v>
-      </c>
-      <c r="G106">
-        <v>0.8087340473332731</v>
-      </c>
-      <c r="H106">
-        <v>0.9014071609929997</v>
-      </c>
-      <c r="I106" t="s">
-        <v>143</v>
-      </c>
-      <c r="J106">
-        <v>0.649574271525752</v>
-      </c>
-      <c r="K106">
-        <v>0.9212483962173839</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
-      <c r="A107" t="s">
-        <v>144</v>
-      </c>
-      <c r="B107" t="s">
-        <v>130</v>
-      </c>
-      <c r="C107">
-        <v>-0.1509649995078519</v>
-      </c>
-      <c r="D107">
-        <v>-0.2970156479975413</v>
-      </c>
-      <c r="E107">
-        <v>-0.004914351018162622</v>
-      </c>
-      <c r="F107">
-        <v>-2.030524212057548</v>
-      </c>
-      <c r="G107">
-        <v>0.04279922221352481</v>
-      </c>
-      <c r="H107">
-        <v>0.2250342889827957</v>
-      </c>
-      <c r="I107" t="s">
-        <v>143</v>
-      </c>
-      <c r="J107">
-        <v>0.086716091840501</v>
-      </c>
-      <c r="K107">
-        <v>0.7232682404227637</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
-      <c r="A108" t="s">
-        <v>145</v>
-      </c>
-      <c r="B108" t="s">
-        <v>130</v>
-      </c>
-      <c r="C108">
-        <v>0.0503862183360709</v>
-      </c>
-      <c r="D108">
-        <v>-0.1444780646768838</v>
-      </c>
-      <c r="E108">
-        <v>0.2452505013490256</v>
-      </c>
-      <c r="F108">
-        <v>0.507942921448066</v>
-      </c>
-      <c r="G108">
-        <v>0.6117035076491797</v>
-      </c>
-      <c r="H108">
-        <v>0.8736494904824352</v>
-      </c>
-      <c r="I108" t="s">
-        <v>143</v>
-      </c>
-      <c r="J108">
-        <v>0.9002152382293892</v>
-      </c>
-      <c r="K108">
-        <v>0.9002152382293892</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
-      <c r="A109" t="s">
-        <v>146</v>
-      </c>
-      <c r="B109" t="s">
-        <v>130</v>
-      </c>
-      <c r="C109">
-        <v>-0.133244629067322</v>
-      </c>
-      <c r="D109">
-        <v>-0.3350121716754236</v>
-      </c>
-      <c r="E109">
-        <v>0.06852291354077958</v>
-      </c>
-      <c r="F109">
-        <v>-1.297280229994255</v>
-      </c>
-      <c r="G109">
-        <v>0.1950960099338417</v>
-      </c>
-      <c r="H109">
-        <v>0.5115858867864171</v>
-      </c>
-      <c r="I109" t="s">
-        <v>143</v>
-      </c>
-      <c r="J109">
-        <v>0.3080029056236571</v>
-      </c>
-      <c r="K109">
-        <v>0.8068623218637324</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
-      <c r="A110" t="s">
-        <v>136</v>
-      </c>
-      <c r="B110" t="s">
-        <v>133</v>
-      </c>
-      <c r="C110">
-        <v>0.005158476606279307</v>
-      </c>
-      <c r="D110">
-        <v>-0.1329107419974876</v>
-      </c>
-      <c r="E110">
-        <v>0.1432276952100462</v>
-      </c>
-      <c r="F110">
-        <v>0.07339390417002253</v>
-      </c>
-      <c r="G110">
-        <v>0.9415202025672604</v>
-      </c>
-      <c r="H110">
-        <v>0.9442169441935748</v>
-      </c>
-      <c r="I110" t="s">
-        <v>137</v>
-      </c>
-      <c r="J110">
-        <v>0.3248810810519941</v>
-      </c>
-      <c r="K110">
-        <v>0.6033505790965604</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
-      <c r="A111" t="s">
-        <v>138</v>
-      </c>
-      <c r="B111" t="s">
-        <v>133</v>
-      </c>
-      <c r="C111">
-        <v>0.1148326677649188</v>
-      </c>
-      <c r="D111">
-        <v>-0.02463949862301265</v>
-      </c>
-      <c r="E111">
-        <v>0.2543048341528502</v>
-      </c>
-      <c r="F111">
-        <v>1.617384585520386</v>
-      </c>
-      <c r="G111">
-        <v>0.1063869164309395</v>
-      </c>
-      <c r="H111">
-        <v>0.6008421903295255</v>
-      </c>
-      <c r="I111" t="s">
-        <v>137</v>
-      </c>
-      <c r="J111">
-        <v>0.02565299263954542</v>
-      </c>
-      <c r="K111">
-        <v>0.1667444521570452</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="A112" t="s">
-        <v>139</v>
-      </c>
-      <c r="B112" t="s">
-        <v>133</v>
-      </c>
-      <c r="C112">
-        <v>-0.09228505531478759</v>
-      </c>
-      <c r="D112">
-        <v>-0.2337143772851205</v>
-      </c>
-      <c r="E112">
-        <v>0.04914426665554536</v>
-      </c>
-      <c r="F112">
-        <v>-1.281820785587264</v>
-      </c>
-      <c r="G112">
-        <v>0.2004628158049568</v>
-      </c>
-      <c r="H112">
-        <v>0.3722880864949198</v>
-      </c>
-      <c r="I112" t="s">
-        <v>143</v>
-      </c>
-      <c r="J112">
-        <v>0.04684395044940116</v>
-      </c>
-      <c r="K112">
-        <v>0.1665219219426752</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
-      <c r="A113" t="s">
-        <v>140</v>
-      </c>
-      <c r="B113" t="s">
-        <v>133</v>
-      </c>
-      <c r="C113">
-        <v>-0.09292330226770337</v>
-      </c>
-      <c r="D113">
-        <v>-0.2553433694902966</v>
-      </c>
-      <c r="E113">
-        <v>0.06949676495488982</v>
-      </c>
-      <c r="F113">
-        <v>-1.123881031517856</v>
-      </c>
-      <c r="G113">
-        <v>0.2615694187600892</v>
-      </c>
-      <c r="H113">
-        <v>0.85010061097029</v>
-      </c>
-      <c r="I113" t="s">
-        <v>143</v>
-      </c>
-      <c r="J113">
-        <v>0.02581617650790154</v>
-      </c>
-      <c r="K113">
-        <v>0.08390257365067999</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
-      <c r="A114" t="s">
-        <v>141</v>
-      </c>
-      <c r="B114" t="s">
-        <v>133</v>
-      </c>
-      <c r="C114">
-        <v>0.005751915757136039</v>
-      </c>
-      <c r="D114">
-        <v>-0.1368217198973957</v>
-      </c>
-      <c r="E114">
-        <v>0.1483255514116678</v>
-      </c>
-      <c r="F114">
-        <v>0.07925171781638198</v>
-      </c>
-      <c r="G114">
-        <v>0.9368621540736652</v>
-      </c>
-      <c r="H114">
-        <v>0.9919088267494406</v>
-      </c>
-      <c r="I114" t="s">
-        <v>137</v>
-      </c>
-      <c r="J114">
-        <v>0.4120388957233302</v>
-      </c>
-      <c r="K114">
-        <v>0.9395313521223855</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
-      <c r="A115" t="s">
-        <v>142</v>
-      </c>
-      <c r="B115" t="s">
-        <v>133</v>
-      </c>
-      <c r="C115">
-        <v>-0.1039222754015034</v>
-      </c>
-      <c r="D115">
-        <v>-0.2476598727368496</v>
-      </c>
-      <c r="E115">
-        <v>0.03981532193384271</v>
-      </c>
-      <c r="F115">
-        <v>-1.420278975504971</v>
-      </c>
-      <c r="G115">
-        <v>0.1561111495898046</v>
-      </c>
-      <c r="H115">
-        <v>0.5867252102342169</v>
-      </c>
-      <c r="I115" t="s">
-        <v>143</v>
-      </c>
-      <c r="J115">
-        <v>0.7086526124749106</v>
-      </c>
-      <c r="K115">
-        <v>0.9212483962173839</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
-      <c r="A116" t="s">
-        <v>144</v>
-      </c>
-      <c r="B116" t="s">
-        <v>133</v>
-      </c>
-      <c r="C116">
-        <v>-0.1032840284485877</v>
-      </c>
-      <c r="D116">
-        <v>-0.249334676938277</v>
-      </c>
-      <c r="E116">
-        <v>0.04276662004110166</v>
-      </c>
-      <c r="F116">
-        <v>-1.389200948348229</v>
-      </c>
-      <c r="G116">
-        <v>0.1653517505540951</v>
-      </c>
-      <c r="H116">
-        <v>0.3582621262005393</v>
-      </c>
-      <c r="I116" t="s">
-        <v>137</v>
-      </c>
-      <c r="J116">
-        <v>0.9408635641011719</v>
-      </c>
-      <c r="K116">
-        <v>0.9408635641011719</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" t="s">
-        <v>145</v>
-      </c>
-      <c r="B117" t="s">
-        <v>133</v>
-      </c>
-      <c r="C117">
-        <v>-0.1096741911586395</v>
-      </c>
-      <c r="D117">
-        <v>-0.3045384741715942</v>
-      </c>
-      <c r="E117">
-        <v>0.0851900918543152</v>
-      </c>
-      <c r="F117">
-        <v>-1.10562433348351</v>
-      </c>
-      <c r="G117">
-        <v>0.2693879529904121</v>
-      </c>
-      <c r="H117">
-        <v>0.6577528921060141</v>
-      </c>
-      <c r="I117" t="s">
-        <v>143</v>
-      </c>
-      <c r="J117">
-        <v>0.35652453354313</v>
-      </c>
-      <c r="K117">
-        <v>0.868457651346254</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
-      <c r="A118" t="s">
-        <v>146</v>
-      </c>
-      <c r="B118" t="s">
-        <v>133</v>
-      </c>
-      <c r="C118">
-        <v>0.0006382469529157778</v>
-      </c>
-      <c r="D118">
-        <v>-0.2011292956551858</v>
-      </c>
-      <c r="E118">
-        <v>0.2024057895610174</v>
-      </c>
-      <c r="F118">
-        <v>0.006214022731478146</v>
-      </c>
-      <c r="G118">
-        <v>0.9950442841587558</v>
-      </c>
-      <c r="H118">
-        <v>0.9950442841587558</v>
-      </c>
-      <c r="I118" t="s">
-        <v>137</v>
-      </c>
-      <c r="J118">
-        <v>0.7447959894126761</v>
-      </c>
-      <c r="K118">
-        <v>0.8068623218637324</v>
+        <v>0.7637718376832046</v>
       </c>
     </row>
   </sheetData>
@@ -6550,1250 +5491,1250 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B2">
-        <v>-0.1535613569776431</v>
+        <v>-0.2852253470863059</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H2">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B3">
-        <v>0.1921679586552427</v>
+        <v>0.2084891236038876</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B4">
-        <v>-0.07794234782998638</v>
+        <v>0.06644768174709738</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H4">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B5">
-        <v>-0.03945403950390909</v>
+        <v>-0.01447786649466187</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H5">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B6">
-        <v>0.02030106733790561</v>
+        <v>0.0105955646086881</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H6">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B7">
-        <v>-0.1692430322463701</v>
+        <v>-0.109738729478648</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H7">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B8">
-        <v>-0.07243559958804847</v>
+        <v>0.02594143102747733</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F8" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H8">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B9">
-        <v>0.008849753561884787</v>
+        <v>0.03561682584207024</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F9" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H9">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B10">
-        <v>0.05842394211105128</v>
+        <v>0.07913359319407803</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F10" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H10">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B11">
-        <v>-0.4873891663870092</v>
+        <v>-0.3598369567602057</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H11">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B12">
-        <v>0.02523638720124165</v>
+        <v>0.0516770866591202</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H12">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B13">
-        <v>-0.1019202366967778</v>
+        <v>-0.01034512909926953</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H13">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B14">
-        <v>0.1278199084287205</v>
+        <v>0.1311214376424162</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B15">
-        <v>0.03475988970066048</v>
+        <v>-0.003569227261912618</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H15">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B16">
-        <v>-0.4869640410369019</v>
+        <v>-0.41431666601947</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F16" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H16">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B17">
-        <v>-0.03294488325635608</v>
+        <v>-0.09249894701671982</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F17" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H17">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B18">
-        <v>0.04769560183222415</v>
+        <v>0.1091053453341327</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H18">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B19">
-        <v>0.02803448182272692</v>
+        <v>0.09139568634965256</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H19">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B20">
-        <v>-0.0426659686524916</v>
+        <v>0.009554462776865983</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H20">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B21">
-        <v>0.02188608850486541</v>
+        <v>-0.0971675322439656</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H21">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B22">
-        <v>-0.008622739031344896</v>
+        <v>-0.3595126356317794</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H22">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B23">
-        <v>-0.1196089081578836</v>
+        <v>-0.08774969953387152</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H23">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B24">
-        <v>0.1591435225501128</v>
+        <v>0.1740879677635165</v>
       </c>
       <c r="C24" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E24" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H24">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B25">
-        <v>0.1247535095816768</v>
+        <v>0.09277382324364071</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F25" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H25">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B26">
-        <v>-0.1124523396630547</v>
+        <v>0.01332529175805057</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E26" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B27">
-        <v>0.1121494462811274</v>
+        <v>0.08784559800771559</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E27" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H27">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B28">
-        <v>0.05222358172923365</v>
+        <v>0.07644964671857142</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E28" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H28">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B29">
-        <v>-0.01895992187145791</v>
+        <v>-0.001579195887323822</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E29" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H29">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B30">
-        <v>0.1047339537334842</v>
+        <v>0.05575685365099291</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F30" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H30">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B31">
-        <v>0.04280675470089889</v>
+        <v>0.09859246759428332</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F31" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H31">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B32">
-        <v>0.03383251415241947</v>
+        <v>0.1257008403925932</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F32" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H32">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B33">
-        <v>0.146249996513723</v>
+        <v>0.06244211266049099</v>
       </c>
       <c r="C33" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F33" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H33">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B34">
-        <v>0.07644445537047016</v>
+        <v>0.03298931143332066</v>
       </c>
       <c r="C34" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F34" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B35">
-        <v>0.05709616142007341</v>
+        <v>0.0277031716650511</v>
       </c>
       <c r="C35" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E35" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H35">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B36">
-        <v>0.1701649075100316</v>
+        <v>0.1413441417880378</v>
       </c>
       <c r="C36" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E36" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F36" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H36">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B37">
-        <v>0.1217125708522324</v>
+        <v>0.1369129250464843</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E37" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F37" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H37">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B38">
-        <v>-0.08490811821087668</v>
+        <v>-0.1175151884619522</v>
       </c>
       <c r="C38" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E38" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H38">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B39">
-        <v>-0.1287773304456785</v>
+        <v>-0.06145143533393014</v>
       </c>
       <c r="C39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F39" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H39">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B40">
-        <v>0.02316326289229437</v>
+        <v>0.08746312662143613</v>
       </c>
       <c r="C40" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E40" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F40" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H40">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B41">
-        <v>-0.0935036195506472</v>
+        <v>-0.1628801835026032</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F41" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H41">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B42">
-        <v>-0.01451568012411337</v>
+        <v>-0.294802758791287</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F42" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H42">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B43">
-        <v>0.08647240774086097</v>
+        <v>0.05054120524502694</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E43" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F43" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H43">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B44">
-        <v>-0.2050929122799053</v>
+        <v>-0.1013574390715152</v>
       </c>
       <c r="C44" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E44" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F44" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H44">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B45">
-        <v>0.0004545852996381175</v>
+        <v>0.07510562600330517</v>
       </c>
       <c r="C45" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E45" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F45" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H45">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B46">
-        <v>0.01243499901610845</v>
+        <v>0.06125237888961736</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E46" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F46" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H46">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B47">
-        <v>0.1687588176164418</v>
+        <v>0.06318952694742001</v>
       </c>
       <c r="C47" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E47" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H47">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B48">
-        <v>0.3057258041015859</v>
+        <v>0.2473408363257912</v>
       </c>
       <c r="C48" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E48" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F48" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H48">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B49">
-        <v>0.08746591129153056</v>
+        <v>0.04412984713459744</v>
       </c>
       <c r="C49" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E49" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F49" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G49" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H49">
-        <v>0.02069808326065618</v>
+        <v>0.03065890032230952</v>
       </c>
     </row>
   </sheetData>
@@ -7834,10 +6775,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
         <v>106</v>
@@ -7855,15 +6796,15 @@
         <v>112</v>
       </c>
       <c r="H2">
-        <v>0.4887640449438202</v>
+        <v>0.6853932584269663</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
         <v>118</v>
@@ -7881,15 +6822,15 @@
         <v>115</v>
       </c>
       <c r="H3">
-        <v>0.6701030927835051</v>
+        <v>0.6907216494845361</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
@@ -7907,15 +6848,15 @@
         <v>118</v>
       </c>
       <c r="H4">
-        <v>0.4745762711864407</v>
+        <v>0.6271186440677966</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
         <v>100</v>
@@ -7930,18 +6871,18 @@
         <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="H5">
-        <v>0.2683982683982684</v>
+        <v>0.5411255411255411</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
         <v>97</v>
@@ -7956,21 +6897,21 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>0.5366666666666666</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="D7">
         <v>73</v>
@@ -7982,18 +6923,18 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H7">
-        <v>0.726027397260274</v>
+        <v>0.6301369863013698</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
         <v>124</v>
@@ -8008,21 +6949,21 @@
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H8">
-        <v>0.4888888888888889</v>
+        <v>0.5444444444444444</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="D9">
         <v>43</v>
@@ -8042,10 +6983,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
         <v>112</v>
@@ -8060,18 +7001,18 @@
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H10">
-        <v>0.4126984126984127</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C11" t="s">
         <v>103</v>
@@ -8086,18 +7027,18 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H11">
-        <v>0.4465116279069767</v>
+        <v>0.5906976744186047</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C12" t="s">
         <v>121</v>
@@ -8112,18 +7053,18 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>0.6559139784946236</v>
+        <v>0.6236559139784946</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
         <v>109</v>
@@ -8138,21 +7079,21 @@
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>0.4509803921568628</v>
+        <v>0.3660130718954248</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="D14">
         <v>68</v>
@@ -8164,18 +7105,18 @@
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H14">
-        <v>0.3823529411764706</v>
+        <v>0.3970588235294117</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
         <v>115</v>
@@ -8190,18 +7131,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>0.625</v>
+        <v>0.5795454545454546</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
         <v>109</v>
@@ -8219,18 +7160,18 @@
         <v>115</v>
       </c>
       <c r="H16">
-        <v>0.6491228070175439</v>
+        <v>0.5964912280701754</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D17">
         <v>43</v>
@@ -8242,18 +7183,18 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>0.5348837209302325</v>
+        <v>0.7674418604651163</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
         <v>121</v>
@@ -8268,7 +7209,7 @@
         <v>3</v>
       </c>
       <c r="G18" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H18">
         <v>0.7457627118644068</v>
@@ -8276,10 +7217,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
         <v>103</v>
@@ -8297,15 +7238,15 @@
         <v>97</v>
       </c>
       <c r="H19">
-        <v>0.355072463768116</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
         <v>112</v>
@@ -8323,15 +7264,15 @@
         <v>124</v>
       </c>
       <c r="H20">
-        <v>0.3636363636363636</v>
+        <v>0.3181818181818182</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
         <v>97</v>
@@ -8346,18 +7287,18 @@
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H21">
-        <v>0.6037735849056604</v>
+        <v>0.5849056603773585</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
         <v>118</v>
@@ -8372,21 +7313,21 @@
         <v>6</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>0.4556962025316456</v>
+        <v>0.2151898734177215</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="D23">
         <v>51</v>
@@ -8401,15 +7342,15 @@
         <v>112</v>
       </c>
       <c r="H23">
-        <v>0.2549019607843137</v>
+        <v>0.3137254901960784</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
         <v>106</v>
@@ -8424,18 +7365,18 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H24">
-        <v>0.3065693430656934</v>
+        <v>0.4379562043795621</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
@@ -8450,21 +7391,21 @@
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H25">
-        <v>0.1955307262569832</v>
+        <v>0.2849162011173184</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="D26">
         <v>47</v>
@@ -8476,21 +7417,21 @@
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="H26">
-        <v>0.2127659574468085</v>
+        <v>0.2978723404255319</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D27">
         <v>39</v>
@@ -8502,21 +7443,21 @@
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>0.5384615384615384</v>
+        <v>0.4615384615384616</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="D28">
         <v>48</v>
@@ -8531,15 +7472,15 @@
         <v>118</v>
       </c>
       <c r="H28">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B29" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
         <v>124</v>
@@ -8554,21 +7495,21 @@
         <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H29">
-        <v>0.2962962962962963</v>
+        <v>0.2592592592592592</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D30">
         <v>46</v>
@@ -8583,7 +7524,7 @@
         <v>112</v>
       </c>
       <c r="H30">
-        <v>0.2391304347826087</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
   </sheetData>
@@ -8609,46 +7550,46 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -8674,541 +7615,541 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C9" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B10" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B11" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B14" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B15" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B16" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B17" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C17" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B18" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C21" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C27" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C28" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C29" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C30" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C31" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C33" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C35" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C41" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C43" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C45" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C47" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B50" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C50" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F5/c_data/F5.xlsx
+++ b/04_Figures/F5/c_data/F5.xlsx
@@ -514,7 +514,7 @@
     <t>01_Processing/07_Module_Characterisation/c_data/module_characterisation.xlsx</t>
   </si>
   <si>
-    <t>344d4e14a48a06a4f63049c9e6502cfc</t>
+    <t>ab7c9e8b5f1a9c5d7052598a2a9b1efd</t>
   </si>
   <si>
     <t>module_detail</t>
